--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Reports\Camera Reports\Dashboard\Brads Towing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Brads Towing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D90888F-2669-4946-880D-73034B4973E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9A42DAC-298F-43BD-B2C3-D942396D2818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="23280" windowHeight="14535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRIVE-ALERTS" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8605" uniqueCount="3159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8936" uniqueCount="3282">
   <si>
     <t>DRIVE ALERTS</t>
   </si>
@@ -3787,6 +3787,12 @@
     <t>01/23/26 09:00 EST</t>
   </si>
   <si>
+    <t>281474995729932-1769176819226</t>
+  </si>
+  <si>
+    <t>01/26/26 12:40 EST</t>
+  </si>
+  <si>
     <t>281474995852965-1769176819203</t>
   </si>
   <si>
@@ -3796,12 +3802,6 @@
     <t>01/26/26 12:30 EST</t>
   </si>
   <si>
-    <t>281474995729932-1769176819226</t>
-  </si>
-  <si>
-    <t>01/26/26 12:40 EST</t>
-  </si>
-  <si>
     <t>01/23/26 09:36 EST</t>
   </si>
   <si>
@@ -8887,31 +8887,13 @@
     <t>03/13/26 09:58 EDT</t>
   </si>
   <si>
-    <t>281474995757668-1773375034878</t>
-  </si>
-  <si>
-    <t>03/13/26 00:51 EDT</t>
-  </si>
-  <si>
-    <t>281474995714975-1773377474475</t>
-  </si>
-  <si>
-    <t>3.6mi NE of Gladstone MO</t>
-  </si>
-  <si>
     <t>03/13/26 08:09 EDT</t>
   </si>
   <si>
     <t>281474995718521-1773403743144</t>
   </si>
   <si>
-    <t>03/13/26 08:39 EDT</t>
-  </si>
-  <si>
-    <t>281474995718521-1773405576637</t>
-  </si>
-  <si>
-    <t>5.4mi NE of Parkville MO</t>
+    <t>03/16/26 18:17 EDT</t>
   </si>
   <si>
     <t>03/13/26 08:53 EDT</t>
@@ -8920,10 +8902,7 @@
     <t>281474995771683-1773406382086</t>
   </si>
   <si>
-    <t>03/13/26 08:57 EDT</t>
-  </si>
-  <si>
-    <t>281474995718521-1773406637503</t>
+    <t>03/16/26 18:19 EDT</t>
   </si>
   <si>
     <t>03/13/26 09:11 EDT</t>
@@ -8941,55 +8920,7 @@
     <t>3.9mi E of St. Joseph MO</t>
   </si>
   <si>
-    <t>281474995728369-1773407867957</t>
-  </si>
-  <si>
-    <t>3.8mi E of St. Joseph MO</t>
-  </si>
-  <si>
-    <t>281474995728369-1773407878824</t>
-  </si>
-  <si>
-    <t>03/13/26 09:18 EDT</t>
-  </si>
-  <si>
-    <t>281474995728369-1773407889421</t>
-  </si>
-  <si>
-    <t>4mi E of St. Joseph MO</t>
-  </si>
-  <si>
-    <t>281474995728369-1773407900219</t>
-  </si>
-  <si>
-    <t>4.1mi E of St. Joseph MO</t>
-  </si>
-  <si>
-    <t>281474995728369-1773407910619</t>
-  </si>
-  <si>
-    <t>4.3mi E of St. Joseph MO</t>
-  </si>
-  <si>
-    <t>281474995728369-1773407923409</t>
-  </si>
-  <si>
-    <t>4.5mi E of St. Joseph MO</t>
-  </si>
-  <si>
-    <t>281474995728369-1773407933605</t>
-  </si>
-  <si>
-    <t>4.7mi E of St. Joseph MO</t>
-  </si>
-  <si>
-    <t>03/13/26 09:19 EDT</t>
-  </si>
-  <si>
-    <t>281474995728369-1773407944804</t>
-  </si>
-  <si>
-    <t>4.9mi E of St. Joseph MO</t>
+    <t>03/16/26 18:52 EDT</t>
   </si>
   <si>
     <t>03/13/26 09:50 EDT</t>
@@ -8998,12 +8929,18 @@
     <t>281474995772256-1773409805590</t>
   </si>
   <si>
+    <t>03/16/26 18:21 EDT</t>
+  </si>
+  <si>
     <t>03/13/26 10:11 EDT</t>
   </si>
   <si>
     <t>281474995731919-1773411078375</t>
   </si>
   <si>
+    <t>03/16/26 18:28 EDT</t>
+  </si>
+  <si>
     <t>03/13/26 10:12 EDT</t>
   </si>
   <si>
@@ -9016,19 +8953,19 @@
     <t>2.5mi NE of Lee's Summit MO</t>
   </si>
   <si>
+    <t>03/16/26 18:30 EDT</t>
+  </si>
+  <si>
     <t>281474995832347-1773411426703</t>
   </si>
   <si>
     <t>1.4mi NW of Blue Springs MO</t>
   </si>
   <si>
-    <t>03/13/26 10:24 EDT</t>
-  </si>
-  <si>
-    <t>281474997805323-1773411853287</t>
-  </si>
-  <si>
-    <t>3.1mi SE of Smithville MO</t>
+    <t>03/16/26 18:33 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 18:54 EDT</t>
   </si>
   <si>
     <t>03/13/26 10:32 EDT</t>
@@ -9040,58 +8977,7 @@
     <t>0.6mi N of Raymore MO</t>
   </si>
   <si>
-    <t>03/13/26 10:33 EDT</t>
-  </si>
-  <si>
-    <t>281474995731919-1773412391015</t>
-  </si>
-  <si>
-    <t>03/13/26 10:38 EDT</t>
-  </si>
-  <si>
-    <t>281474995772256-1773412714824</t>
-  </si>
-  <si>
-    <t>1mi NE of Belton MO</t>
-  </si>
-  <si>
-    <t>03/13/26 10:44 EDT</t>
-  </si>
-  <si>
-    <t>281474995772256-1773413063096</t>
-  </si>
-  <si>
-    <t>03/13/26 10:52 EDT</t>
-  </si>
-  <si>
-    <t>281474995832347-1773413551129</t>
-  </si>
-  <si>
-    <t>1.3mi NE of Blue Springs MO</t>
-  </si>
-  <si>
-    <t>03/13/26 10:56 EDT</t>
-  </si>
-  <si>
-    <t>281474995718521-1773413767446</t>
-  </si>
-  <si>
-    <t>03/13/26 11:17 EDT</t>
-  </si>
-  <si>
-    <t>281474995832347-1773415058088</t>
-  </si>
-  <si>
-    <t>2.8mi NW of Leawood KS</t>
-  </si>
-  <si>
-    <t>03/13/26 11:22 EDT</t>
-  </si>
-  <si>
-    <t>281474995832347-1773415358213</t>
-  </si>
-  <si>
-    <t>3.3mi SE of Lenexa KS</t>
+    <t>03/16/26 18:56 EDT</t>
   </si>
   <si>
     <t>03/13/26 11:41 EDT</t>
@@ -9103,400 +8989,883 @@
     <t>1.3mi SW of Gladstone MO</t>
   </si>
   <si>
-    <t>03/13/26 11:51 EDT</t>
-  </si>
-  <si>
-    <t>281474995718105-1773417099537</t>
-  </si>
-  <si>
-    <t>2.5mi NE of Kansas City MO</t>
-  </si>
-  <si>
-    <t>03/13/26 12:08 EDT</t>
-  </si>
-  <si>
-    <t>281474995837577-1773418100955</t>
-  </si>
-  <si>
-    <t>2.8mi NE of Prairie Village KS</t>
-  </si>
-  <si>
-    <t>03/13/26 12:13 EDT</t>
-  </si>
-  <si>
-    <t>281474995772256-1773418380282</t>
-  </si>
-  <si>
     <t>03/13/26 12:31 EDT</t>
   </si>
   <si>
     <t>281474995966045-1773419506382</t>
   </si>
   <si>
-    <t>03/13/26 12:32 EDT</t>
-  </si>
-  <si>
-    <t>281474995966045-1773419562375</t>
-  </si>
-  <si>
-    <t>03/13/26 12:40 EDT</t>
-  </si>
-  <si>
-    <t>281474995966045-1773420028677</t>
-  </si>
-  <si>
-    <t>281474995966045-1773420041476</t>
+    <t>03/16/26 19:02 EDT</t>
+  </si>
+  <si>
+    <t>03/13/26 13:10 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773421828849</t>
+  </si>
+  <si>
+    <t>03/13/26 14:31 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773426665181</t>
+  </si>
+  <si>
+    <t>2.3mi S of Gladstone MO</t>
+  </si>
+  <si>
+    <t>03/13/26 15:32 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773430326698</t>
+  </si>
+  <si>
+    <t>03/13/26 16:40 EDT</t>
+  </si>
+  <si>
+    <t>281474995757668-1773434435199</t>
+  </si>
+  <si>
+    <t>03/16/26 18:08 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 02:23 EDT</t>
+  </si>
+  <si>
+    <t>281474995757668-1773469407961</t>
+  </si>
+  <si>
+    <t>03/16/26 17:58 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 10:18 EDT</t>
+  </si>
+  <si>
+    <t>281474995713058-1773497934241</t>
+  </si>
+  <si>
+    <t>3mi SE of De Soto KS</t>
+  </si>
+  <si>
+    <t>03/16/26 18:39 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 11:28 EDT</t>
+  </si>
+  <si>
+    <t>#554</t>
+  </si>
+  <si>
+    <t>281474995729932-1773502091607</t>
+  </si>
+  <si>
+    <t>03/14/26 12:13 EDT</t>
+  </si>
+  <si>
+    <t>281474995837577-1773504791552</t>
+  </si>
+  <si>
+    <t>3.7mi S of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/16/26 18:42 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 12:37 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773506230869</t>
+  </si>
+  <si>
+    <t>03/14/26 15:28 EDT</t>
+  </si>
+  <si>
+    <t>281474995852965-1773516525043</t>
+  </si>
+  <si>
+    <t>03/16/26 18:44 EDT</t>
+  </si>
+  <si>
+    <t>03/14/26 16:24 EDT</t>
+  </si>
+  <si>
+    <t>281474995837577-1773519891550</t>
+  </si>
+  <si>
+    <t>3.5mi E of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/16/26 19:07 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 06:11 EDT</t>
+  </si>
+  <si>
+    <t>281474995832347-1773569466984</t>
+  </si>
+  <si>
+    <t>03/16/26 18:00 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 18:02 EDT</t>
+  </si>
+  <si>
+    <t>03/15/26 15:17 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773602259200</t>
+  </si>
+  <si>
+    <t>5.7mi N of Gladstone MO</t>
+  </si>
+  <si>
+    <t>03/15/26 16:18 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773605926914</t>
+  </si>
+  <si>
+    <t>03/15/26 23:23 EDT</t>
+  </si>
+  <si>
+    <t>281474995728019-1773631393962</t>
+  </si>
+  <si>
+    <t>03/16/26 18:05 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 00:59 EDT</t>
+  </si>
+  <si>
+    <t>281474995728019-1773637196717</t>
+  </si>
+  <si>
+    <t>2.3mi NW of Liberty MO</t>
+  </si>
+  <si>
+    <t>03/17/26 12:07 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 12:08 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 04:19 EDT</t>
+  </si>
+  <si>
+    <t>281474995757668-1773649170951</t>
+  </si>
+  <si>
+    <t>03/17/26 11:31 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 06:55 EDT</t>
+  </si>
+  <si>
+    <t>281474995832347-1773658525956</t>
+  </si>
+  <si>
+    <t>1.9mi SW of Independence MO</t>
+  </si>
+  <si>
+    <t>03/17/26 11:33 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 15:41 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 08:40 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773664850565</t>
+  </si>
+  <si>
+    <t>3mi W of Liberty MO</t>
+  </si>
+  <si>
+    <t>03/16/26 10:32 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773671528915</t>
+  </si>
+  <si>
+    <t>2.8mi W of Liberty MO</t>
+  </si>
+  <si>
+    <t>03/16/26 10:47 EDT</t>
+  </si>
+  <si>
+    <t>281474995731919-1773672436963</t>
+  </si>
+  <si>
+    <t>4.3mi NE of Raytown MO</t>
+  </si>
+  <si>
+    <t>03/16/26 10:51 EDT</t>
+  </si>
+  <si>
+    <t>281474995718521-1773672715752</t>
+  </si>
+  <si>
+    <t>9mi SW of Smithville MO</t>
+  </si>
+  <si>
+    <t>03/17/26 11:44 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 11:40 EDT</t>
+  </si>
+  <si>
+    <t>281474995772256-1773675651819</t>
+  </si>
+  <si>
+    <t>3.3mi S of Liberty MO</t>
+  </si>
+  <si>
+    <t>03/17/26 11:47 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 11:43 EDT</t>
+  </si>
+  <si>
+    <t>281474995713058-1773675812935</t>
+  </si>
+  <si>
+    <t>03/17/26 11:51 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 11:44 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773675842512</t>
+  </si>
+  <si>
+    <t>03/16/26 12:45 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773679510896</t>
+  </si>
+  <si>
+    <t>03/16/26 13:51 EDT</t>
+  </si>
+  <si>
+    <t>281474995771683-1773683476855</t>
+  </si>
+  <si>
+    <t>03/17/26 11:52 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 13:53 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773683615355</t>
+  </si>
+  <si>
+    <t>03/16/26 14:03 EDT</t>
+  </si>
+  <si>
+    <t>281474995966045-1773684180023</t>
+  </si>
+  <si>
+    <t>4.1mi NE of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/16/26 14:17 EDT</t>
+  </si>
+  <si>
+    <t>281474995731919-1773685069204</t>
+  </si>
+  <si>
+    <t>2.8mi S of Gladstone MO</t>
+  </si>
+  <si>
+    <t>03/17/26 11:59 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 15:03 EDT</t>
+  </si>
+  <si>
+    <t>281474995837577-1773687790023</t>
+  </si>
+  <si>
+    <t>03/17/26 11:55 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 15:08 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773688080266</t>
+  </si>
+  <si>
+    <t>03/16/26 17:54 EDT</t>
+  </si>
+  <si>
+    <t>281474995966045-1773698083567</t>
+  </si>
+  <si>
+    <t>03/16/26 18:55 EDT</t>
+  </si>
+  <si>
+    <t>281474995966045-1773701753922</t>
+  </si>
+  <si>
+    <t>3.5mi NE of Roeland Park KS</t>
+  </si>
+  <si>
+    <t>03/16/26 19:01 EDT</t>
+  </si>
+  <si>
+    <t>281474995718105-1773702103558</t>
+  </si>
+  <si>
+    <t>03/17/26 12:01 EDT</t>
+  </si>
+  <si>
+    <t>03/16/26 19:25 EDT</t>
+  </si>
+  <si>
+    <t>281474995771683-1773703553967</t>
+  </si>
+  <si>
+    <t>03/17/26 11:35 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 07:56 EDT</t>
+  </si>
+  <si>
+    <t>281474995718521-1773748615417</t>
+  </si>
+  <si>
+    <t>03/18/26 15:44 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 08:10 EDT</t>
+  </si>
+  <si>
+    <t>281474995772256-1773749452321</t>
+  </si>
+  <si>
+    <t>03/18/26 15:47 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 09:35 EDT</t>
+  </si>
+  <si>
+    <t>281474995771683-1773754510057</t>
+  </si>
+  <si>
+    <t>03/18/26 15:54 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 09:45 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773755108980</t>
+  </si>
+  <si>
+    <t>03/17/26 10:40 EDT</t>
+  </si>
+  <si>
+    <t>281474995837577-1773758416494</t>
+  </si>
+  <si>
+    <t>4mi N of Roeland Park KS</t>
+  </si>
+  <si>
+    <t>03/18/26 18:45 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 10:52 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773759125513</t>
+  </si>
+  <si>
+    <t>03/17/26 11:21 EDT</t>
+  </si>
+  <si>
+    <t>281474995718105-1773760881910</t>
+  </si>
+  <si>
+    <t>1.6mi SE of Raytown MO</t>
+  </si>
+  <si>
+    <t>03/18/26 15:57 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 11:56 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773763003668</t>
+  </si>
+  <si>
+    <t>2.8mi SW of Gladstone MO</t>
+  </si>
+  <si>
+    <t>03/17/26 12:05 EDT</t>
+  </si>
+  <si>
+    <t>281474995837577-1773763532432</t>
+  </si>
+  <si>
+    <t>4.5mi N of Lee's Summit MO</t>
+  </si>
+  <si>
+    <t>03/18/26 16:01 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 12:22 EDT</t>
+  </si>
+  <si>
+    <t>281474995852965-1773764561403</t>
   </si>
   <si>
     <t>4.7mi S of Smithville MO</t>
   </si>
   <si>
-    <t>03/13/26 12:42 EDT</t>
-  </si>
-  <si>
-    <t>281474995966045-1773420140384</t>
-  </si>
-  <si>
-    <t>281474995713058-1773420161971</t>
-  </si>
-  <si>
-    <t>0.5mi S of De Soto KS</t>
-  </si>
-  <si>
-    <t>03/13/26 12:45 EDT</t>
-  </si>
-  <si>
-    <t>281474995966045-1773420348017</t>
-  </si>
-  <si>
-    <t>03/13/26 12:47 EDT</t>
-  </si>
-  <si>
-    <t>281474995729254-1773420430253</t>
-  </si>
-  <si>
-    <t>03/13/26 12:49 EDT</t>
-  </si>
-  <si>
-    <t>281474995729254-1773420564805</t>
-  </si>
-  <si>
-    <t>2.9mi N of Kansas City MO</t>
-  </si>
-  <si>
-    <t>03/13/26 13:10 EDT</t>
-  </si>
-  <si>
-    <t>281474995729932-1773421828849</t>
-  </si>
-  <si>
-    <t>03/13/26 13:17 EDT</t>
-  </si>
-  <si>
-    <t>281474995832347-1773422239690</t>
-  </si>
-  <si>
-    <t>03/13/26 13:26 EDT</t>
-  </si>
-  <si>
-    <t>281474995718521-1773422785237</t>
-  </si>
-  <si>
-    <t>2.9mi NE of Gladstone MO</t>
-  </si>
-  <si>
-    <t>03/13/26 14:20 EDT</t>
-  </si>
-  <si>
-    <t>281474995832347-1773426056999</t>
-  </si>
-  <si>
-    <t>03/13/26 14:31 EDT</t>
-  </si>
-  <si>
-    <t>281474995729932-1773426665181</t>
-  </si>
-  <si>
-    <t>2.3mi S of Gladstone MO</t>
-  </si>
-  <si>
-    <t>03/13/26 14:39 EDT</t>
-  </si>
-  <si>
-    <t>281474995772256-1773427180899</t>
-  </si>
-  <si>
-    <t>03/13/26 14:49 EDT</t>
-  </si>
-  <si>
-    <t>281474995772256-1773427742828</t>
-  </si>
-  <si>
-    <t>5.7mi S of Smithville MO</t>
-  </si>
-  <si>
-    <t>03/13/26 15:28 EDT</t>
-  </si>
-  <si>
-    <t>281474995832347-1773430085701</t>
-  </si>
-  <si>
-    <t>03/13/26 15:32 EDT</t>
-  </si>
-  <si>
-    <t>281474995729932-1773430326698</t>
-  </si>
-  <si>
-    <t>03/13/26 16:03 EDT</t>
-  </si>
-  <si>
-    <t>281474995832347-1773432184591</t>
-  </si>
-  <si>
-    <t>0.9mi N of Roeland Park KS</t>
-  </si>
-  <si>
-    <t>03/13/26 16:09 EDT</t>
-  </si>
-  <si>
-    <t>281474997805323-1773432576663</t>
-  </si>
-  <si>
-    <t>4.2mi NE of Gladstone MO</t>
-  </si>
-  <si>
-    <t>03/13/26 16:12 EDT</t>
-  </si>
-  <si>
-    <t>281474995832347-1773432740885</t>
-  </si>
-  <si>
-    <t>2.2mi SW of Kansas City MO</t>
-  </si>
-  <si>
-    <t>03/13/26 16:40 EDT</t>
-  </si>
-  <si>
-    <t>281474995757668-1773434435199</t>
-  </si>
-  <si>
-    <t>03/13/26 16:51 EDT</t>
-  </si>
-  <si>
-    <t>281474995757668-1773435117217</t>
-  </si>
-  <si>
-    <t>3.5mi S of Liberty MO</t>
-  </si>
-  <si>
-    <t>03/13/26 16:57 EDT</t>
-  </si>
-  <si>
-    <t>281474995757668-1773435478486</t>
-  </si>
-  <si>
-    <t>5.8mi E of Kansas City MO</t>
-  </si>
-  <si>
-    <t>03/13/26 17:35 EDT</t>
-  </si>
-  <si>
-    <t>281474995718105-1773437738085</t>
-  </si>
-  <si>
-    <t>6mi S of Liberty MO</t>
-  </si>
-  <si>
-    <t>03/13/26 17:38 EDT</t>
-  </si>
-  <si>
-    <t>281474997805323-1773437939819</t>
-  </si>
-  <si>
-    <t>3.1mi SW of Raytown MO</t>
-  </si>
-  <si>
-    <t>03/13/26 17:42 EDT</t>
-  </si>
-  <si>
-    <t>281474995718521-1773438144285</t>
-  </si>
-  <si>
-    <t>281474995772256-1773438148144</t>
-  </si>
-  <si>
-    <t>03/13/26 17:43 EDT</t>
-  </si>
-  <si>
-    <t>281474995718521-1773438223612</t>
-  </si>
-  <si>
-    <t>3.5mi NE of Kansas City MO</t>
-  </si>
-  <si>
-    <t>03/13/26 17:49 EDT</t>
-  </si>
-  <si>
-    <t>281474995772256-1773438598265</t>
-  </si>
-  <si>
-    <t>3.5mi S of Kansas City MO</t>
-  </si>
-  <si>
-    <t>03/13/26 18:02 EDT</t>
-  </si>
-  <si>
-    <t>281474997805323-1773439351904</t>
-  </si>
-  <si>
-    <t>6.2mi SE of Smithville MO</t>
-  </si>
-  <si>
-    <t>03/13/26 18:04 EDT</t>
-  </si>
-  <si>
-    <t>281474997805323-1773439447989</t>
-  </si>
-  <si>
-    <t>03/13/26 18:05 EDT</t>
-  </si>
-  <si>
-    <t>281474995832347-1773439525464</t>
-  </si>
-  <si>
-    <t>HARSH-BRAKE</t>
-  </si>
-  <si>
-    <t>03/13/26 18:17 EDT</t>
-  </si>
-  <si>
-    <t>281474995718521-1773440232908</t>
-  </si>
-  <si>
-    <t>03/13/26 18:23 EDT</t>
-  </si>
-  <si>
-    <t>281474995718521-1773440633694</t>
-  </si>
-  <si>
-    <t>03/13/26 18:26 EDT</t>
-  </si>
-  <si>
-    <t>281474995772256-1773440779338</t>
-  </si>
-  <si>
-    <t>0.2mi NE of Merriam KS</t>
-  </si>
-  <si>
-    <t>281474995718521-1773440790662</t>
-  </si>
-  <si>
-    <t>03/13/26 18:28 EDT</t>
-  </si>
-  <si>
-    <t>281474995718521-1773440933830</t>
-  </si>
-  <si>
-    <t>03/13/26 18:48 EDT</t>
-  </si>
-  <si>
-    <t>281474995718521-1773442122319</t>
-  </si>
-  <si>
-    <t>15.6mi NW of Smithville MO</t>
-  </si>
-  <si>
-    <t>03/13/26 18:57 EDT</t>
-  </si>
-  <si>
-    <t>281474995718521-1773442654471</t>
-  </si>
-  <si>
-    <t>11.7mi E of Atchison KS</t>
-  </si>
-  <si>
-    <t>03/13/26 19:04 EDT</t>
-  </si>
-  <si>
-    <t>281474995771683-1773443045654</t>
-  </si>
-  <si>
-    <t>4.6mi SE of Kansas City MO</t>
-  </si>
-  <si>
-    <t>03/13/26 21:13 EDT</t>
-  </si>
-  <si>
-    <t>281474995718521-1773450820089</t>
-  </si>
-  <si>
-    <t>1.7mi E of St. Joseph MO</t>
-  </si>
-  <si>
-    <t>03/13/26 21:21 EDT</t>
-  </si>
-  <si>
-    <t>281474995718521-1773451300534</t>
-  </si>
-  <si>
-    <t>3.8mi SE of St. Joseph MO</t>
-  </si>
-  <si>
-    <t>03/13/26 21:38 EDT</t>
-  </si>
-  <si>
-    <t>281474995714975-1773452288107</t>
-  </si>
-  <si>
-    <t>03/13/26 23:10 EDT</t>
-  </si>
-  <si>
-    <t>281474995757668-1773457853965</t>
-  </si>
-  <si>
-    <t>2.4mi N of Grain Valley MO</t>
-  </si>
-  <si>
-    <t>03/13/26 23:22 EDT</t>
-  </si>
-  <si>
-    <t>281474995757668-1773458548326</t>
-  </si>
-  <si>
-    <t>1.3mi N of Blue Springs MO</t>
-  </si>
-  <si>
-    <t>03/13/26 23:34 EDT</t>
-  </si>
-  <si>
-    <t>281474995757668-1773459269072</t>
-  </si>
-  <si>
-    <t>03/13/26 23:53 EDT</t>
-  </si>
-  <si>
-    <t>281474995757668-1773460396361</t>
-  </si>
-  <si>
-    <t>03/14/26 02:23 EDT</t>
-  </si>
-  <si>
-    <t>281474995757668-1773469407961</t>
-  </si>
-  <si>
-    <t>03/14/26 07:06 EDT</t>
-  </si>
-  <si>
-    <t>281474995772256-1773486384655</t>
-  </si>
-  <si>
-    <t>5.2mi W of Independence MO</t>
-  </si>
-  <si>
-    <t>03/14/26 07:28 EDT</t>
-  </si>
-  <si>
-    <t>281474995772256-1773487689172</t>
+    <t>03/18/26 16:04 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 13:00 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773766811260</t>
+  </si>
+  <si>
+    <t>4.4mi NE of Parkville MO</t>
+  </si>
+  <si>
+    <t>03/17/26 13:06 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773767202178</t>
+  </si>
+  <si>
+    <t>5.2mi NE of Parkville MO</t>
+  </si>
+  <si>
+    <t>03/18/26 16:00 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 13:35 EDT</t>
+  </si>
+  <si>
+    <t>281474995966045-1773768929422</t>
+  </si>
+  <si>
+    <t>9.6mi SE of Winfield KS</t>
+  </si>
+  <si>
+    <t>03/18/26 18:40 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 14:39 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773772754750</t>
+  </si>
+  <si>
+    <t>03/17/26 14:44 EDT</t>
+  </si>
+  <si>
+    <t>281474995966045-1773773073337</t>
+  </si>
+  <si>
+    <t>2.2mi NE of Wichita KS</t>
+  </si>
+  <si>
+    <t>03/17/26 15:20 EDT</t>
+  </si>
+  <si>
+    <t>281474995772256-1773775200136</t>
+  </si>
+  <si>
+    <t>03/18/26 18:36 EDT</t>
+  </si>
+  <si>
+    <t>03/17/26 16:31 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773779479966</t>
+  </si>
+  <si>
+    <t>5.1mi NW of Gladstone MO</t>
+  </si>
+  <si>
+    <t>03/18/26 06:13 EDT</t>
+  </si>
+  <si>
+    <t>281474995718105-1773828782003</t>
+  </si>
+  <si>
+    <t>3.9mi S of Raytown MO</t>
+  </si>
+  <si>
+    <t>03/19/26 12:13 EDT</t>
+  </si>
+  <si>
+    <t>03/18/26 08:26 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773836775817</t>
+  </si>
+  <si>
+    <t>03/18/26 08:49 EDT</t>
+  </si>
+  <si>
+    <t>281474995966045-1773838182531</t>
+  </si>
+  <si>
+    <t>03/18/26 10:01 EDT</t>
+  </si>
+  <si>
+    <t>281474995713058-1773842460953</t>
+  </si>
+  <si>
+    <t>03/18/26 10:02 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773842570551</t>
+  </si>
+  <si>
+    <t>7.8mi N of Parkville MO</t>
+  </si>
+  <si>
+    <t>03/18/26 11:35 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773848154282</t>
+  </si>
+  <si>
+    <t>4.1mi S of Smithville MO</t>
+  </si>
+  <si>
+    <t>03/18/26 13:00 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773853221753</t>
+  </si>
+  <si>
+    <t>2.8mi NW of Gladstone MO</t>
+  </si>
+  <si>
+    <t>03/18/26 14:01 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773856860470</t>
+  </si>
+  <si>
+    <t>03/18/26 15:04 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773860645711</t>
+  </si>
+  <si>
+    <t>2.8mi E of Parkville MO</t>
+  </si>
+  <si>
+    <t>03/19/26 08:23 EDT</t>
+  </si>
+  <si>
+    <t>281474995729254-1773922981459</t>
+  </si>
+  <si>
+    <t>03/20/26 19:59 EDT</t>
+  </si>
+  <si>
+    <t>03/20/26 20:00 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 09:46 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773927989661</t>
+  </si>
+  <si>
+    <t>03/19/26 11:41 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773934896207</t>
+  </si>
+  <si>
+    <t>03/19/26 13:03 EDT</t>
+  </si>
+  <si>
+    <t>281474995837577-1773939797147</t>
+  </si>
+  <si>
+    <t>03/20/26 19:56 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 13:12 EDT</t>
+  </si>
+  <si>
+    <t>281474995757668-1773940362088</t>
+  </si>
+  <si>
+    <t>03/20/26 20:01 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 13:23 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773940992369</t>
+  </si>
+  <si>
+    <t>6mi N of Gladstone MO</t>
+  </si>
+  <si>
+    <t>03/19/26 15:24 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773948279111</t>
+  </si>
+  <si>
+    <t>03/19/26 15:42 EDT</t>
+  </si>
+  <si>
+    <t>281474995837577-1773949329930</t>
+  </si>
+  <si>
+    <t>2mi S of Liberty MO</t>
+  </si>
+  <si>
+    <t>03/20/26 20:05 EDT</t>
+  </si>
+  <si>
+    <t>03/19/26 17:05 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773954310587</t>
+  </si>
+  <si>
+    <t>1.3mi SW of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/19/26 18:09 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1773958193504</t>
+  </si>
+  <si>
+    <t>03/20/26 07:53 EDT</t>
+  </si>
+  <si>
+    <t>281474995718105-1774007616864</t>
+  </si>
+  <si>
+    <t>DEFENSIVE-DRIVING</t>
+  </si>
+  <si>
+    <t>03/20/26 08:01 EDT</t>
+  </si>
+  <si>
+    <t>281474995772256-1774008066970</t>
+  </si>
+  <si>
+    <t>03/20/26 08:15 EDT</t>
+  </si>
+  <si>
+    <t>281474995772256-1774008911513</t>
+  </si>
+  <si>
+    <t>03/20/26 08:22 EDT</t>
+  </si>
+  <si>
+    <t>281474995772256-1774009327602</t>
+  </si>
+  <si>
+    <t>03/20/26 08:27 EDT</t>
+  </si>
+  <si>
+    <t>281474995772256-1774009672007</t>
+  </si>
+  <si>
+    <t>03/20/26 08:28 EDT</t>
+  </si>
+  <si>
+    <t>281474995772256-1774009682408</t>
+  </si>
+  <si>
+    <t>1mi NW of Roeland Park KS</t>
+  </si>
+  <si>
+    <t>281474995772256-1774009701701</t>
+  </si>
+  <si>
+    <t>1.2mi NW of Roeland Park KS</t>
+  </si>
+  <si>
+    <t>03/20/26 08:29 EDT</t>
+  </si>
+  <si>
+    <t>281474995772256-1774009769723</t>
+  </si>
+  <si>
+    <t>03/20/26 08:37 EDT</t>
+  </si>
+  <si>
+    <t>281474995772256-1774010268807</t>
+  </si>
+  <si>
+    <t>3.3mi NE of Olathe KS</t>
+  </si>
+  <si>
+    <t>03/20/26 10:07 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1774015635456</t>
+  </si>
+  <si>
+    <t>2mi N of Smithville MO</t>
+  </si>
+  <si>
+    <t>03/20/26 11:57 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1774022254483</t>
+  </si>
+  <si>
+    <t>3.9mi SW of Gladstone MO</t>
+  </si>
+  <si>
+    <t>03/20/26 12:14 EDT</t>
+  </si>
+  <si>
+    <t>281474995837577-1774023261647</t>
+  </si>
+  <si>
+    <t>4mi S of Liberty MO</t>
+  </si>
+  <si>
+    <t>03/20/26 13:11 EDT</t>
+  </si>
+  <si>
+    <t>281474995837577-1774026697557</t>
+  </si>
+  <si>
+    <t>3.6mi W of Independence MO</t>
+  </si>
+  <si>
+    <t>03/20/26 13:16 EDT</t>
+  </si>
+  <si>
+    <t>281474995837577-1774027012276</t>
+  </si>
+  <si>
+    <t>2.2mi W of Independence MO</t>
+  </si>
+  <si>
+    <t>03/20/26 13:17 EDT</t>
+  </si>
+  <si>
+    <t>281474995837577-1774027038877</t>
+  </si>
+  <si>
+    <t>2.1mi W of Independence MO</t>
+  </si>
+  <si>
+    <t>03/20/26 13:24 EDT</t>
+  </si>
+  <si>
+    <t>281474995729254-1774027446969</t>
+  </si>
+  <si>
+    <t>03/20/26 15:12 EDT</t>
+  </si>
+  <si>
+    <t>281474995837577-1774033975293</t>
+  </si>
+  <si>
+    <t>03/20/26 17:30 EDT</t>
+  </si>
+  <si>
+    <t>281474995771066-1774042219266</t>
+  </si>
+  <si>
+    <t>03/20/26 17:47 EDT</t>
+  </si>
+  <si>
+    <t>281474995731919-1774043230605</t>
+  </si>
+  <si>
+    <t>0.8mi E of Grain Valley MO</t>
+  </si>
+  <si>
+    <t>03/20/26 17:52 EDT</t>
+  </si>
+  <si>
+    <t>281474995731919-1774043550138</t>
+  </si>
+  <si>
+    <t>3mi E of Oak Grove MO</t>
+  </si>
+  <si>
+    <t>281474995731919-1774043571403</t>
+  </si>
+  <si>
+    <t>3.5mi E of Oak Grove MO</t>
+  </si>
+  <si>
+    <t>03/20/26 18:22 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1774045322641</t>
+  </si>
+  <si>
+    <t>2.5mi W of Liberty MO</t>
+  </si>
+  <si>
+    <t>03/21/26 08:25 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1774095906204</t>
+  </si>
+  <si>
+    <t>9.3mi S of St. Joseph MO</t>
+  </si>
+  <si>
+    <t>03/21/26 09:30 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1774099805725</t>
+  </si>
+  <si>
+    <t>03/21/26 11:00 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1774105224575</t>
+  </si>
+  <si>
+    <t>1.3mi NW of Gladstone MO</t>
+  </si>
+  <si>
+    <t>03/21/26 12:31 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1774110682118</t>
+  </si>
+  <si>
+    <t>3.7mi NW of Smithville MO</t>
+  </si>
+  <si>
+    <t>03/21/26 15:02 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1774119737297</t>
+  </si>
+  <si>
+    <t>3.9mi W of Kansas City MO</t>
+  </si>
+  <si>
+    <t>03/21/26 16:10 EDT</t>
+  </si>
+  <si>
+    <t>281474995729932-1774123809028</t>
+  </si>
+  <si>
+    <t>03/21/26 19:10 EDT</t>
+  </si>
+  <si>
+    <t>281474995832347-1774134651196</t>
   </si>
 </sst>
 </file>
@@ -9858,7 +10227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M904"/>
+  <dimension ref="A1:M932"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="15" customWidth="1"/>
@@ -22597,10 +22966,10 @@
         <v>1254</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="D335" s="3" t="s">
         <v>1255</v>
@@ -22609,25 +22978,23 @@
         <v>245</v>
       </c>
       <c r="F335" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="G335" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H335" s="3">
+        <v>39</v>
+      </c>
+      <c r="I335" s="3"/>
+      <c r="J335" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K335" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L335" s="3" t="s">
         <v>1256</v>
-      </c>
-      <c r="G335" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H335" s="3">
-        <v>50</v>
-      </c>
-      <c r="I335" s="3">
-        <v>45</v>
-      </c>
-      <c r="J335" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K335" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L335" s="3" t="s">
-        <v>1257</v>
       </c>
       <c r="M335" s="3"/>
     </row>
@@ -22636,27 +23003,29 @@
         <v>1254</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>140</v>
+        <v>16</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>141</v>
+        <v>17</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="E336" s="3" t="s">
         <v>245</v>
       </c>
       <c r="F336" s="3" t="s">
-        <v>447</v>
+        <v>1258</v>
       </c>
       <c r="G336" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H336" s="3">
-        <v>39</v>
-      </c>
-      <c r="I336" s="3"/>
+        <v>50</v>
+      </c>
+      <c r="I336" s="3">
+        <v>45</v>
+      </c>
       <c r="J336" s="3" t="s">
         <v>22</v>
       </c>
@@ -40873,95 +41242,107 @@
     </row>
     <row r="820" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A820" s="3" t="s">
-        <v>2936</v>
+        <v>2955</v>
       </c>
       <c r="B820" s="3" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C820" s="3" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D820" s="3" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="E820" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F820" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="G820" s="3"/>
+        <v>1000</v>
+      </c>
+      <c r="G820" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H820" s="3">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I820" s="3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J820" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K820" s="3"/>
-      <c r="L820" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K820" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L820" s="3" t="s">
+        <v>2957</v>
+      </c>
       <c r="M820" s="3"/>
     </row>
     <row r="821" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A821" s="3" t="s">
-        <v>2956</v>
+        <v>2958</v>
       </c>
       <c r="B821" s="3" t="s">
-        <v>909</v>
+        <v>178</v>
       </c>
       <c r="C821" s="3" t="s">
-        <v>910</v>
+        <v>179</v>
       </c>
       <c r="D821" s="3" t="s">
-        <v>2957</v>
+        <v>2959</v>
       </c>
       <c r="E821" s="3" t="s">
-        <v>2016</v>
+        <v>19</v>
       </c>
       <c r="F821" s="3" t="s">
-        <v>2958</v>
-      </c>
-      <c r="G821" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="G821" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H821" s="3">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="I821" s="3">
         <v>65</v>
       </c>
       <c r="J821" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K821" s="3"/>
-      <c r="L821" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K821" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L821" s="3" t="s">
+        <v>2960</v>
+      </c>
       <c r="M821" s="3"/>
     </row>
     <row r="822" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A822" s="3" t="s">
-        <v>2959</v>
+        <v>2961</v>
       </c>
       <c r="B822" s="3" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="C822" s="3" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="D822" s="3" t="s">
-        <v>2960</v>
+        <v>2962</v>
       </c>
       <c r="E822" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F822" s="3" t="s">
-        <v>1000</v>
+        <v>1016</v>
       </c>
       <c r="G822" s="3"/>
       <c r="H822" s="3">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="I822" s="3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J822" s="3" t="s">
         <v>70</v>
@@ -40972,104 +41353,122 @@
     </row>
     <row r="823" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A823" s="3" t="s">
-        <v>2961</v>
+        <v>2963</v>
       </c>
       <c r="B823" s="3" t="s">
-        <v>53</v>
+        <v>1563</v>
       </c>
       <c r="C823" s="3" t="s">
-        <v>54</v>
+        <v>1564</v>
       </c>
       <c r="D823" s="3" t="s">
-        <v>2962</v>
+        <v>2964</v>
       </c>
       <c r="E823" s="3" t="s">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="F823" s="3" t="s">
-        <v>2963</v>
-      </c>
-      <c r="G823" s="3"/>
+        <v>2965</v>
+      </c>
+      <c r="G823" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H823" s="3">
-        <v>55</v>
-      </c>
-      <c r="I823" s="3">
-        <v>70</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I823" s="3"/>
       <c r="J823" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K823" s="3"/>
-      <c r="L823" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K823" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L823" s="3" t="s">
+        <v>2966</v>
+      </c>
       <c r="M823" s="3"/>
     </row>
     <row r="824" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A824" s="3" t="s">
-        <v>2964</v>
+        <v>2967</v>
       </c>
       <c r="B824" s="3" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="C824" s="3" t="s">
-        <v>179</v>
+        <v>73</v>
       </c>
       <c r="D824" s="3" t="s">
-        <v>2965</v>
+        <v>2968</v>
       </c>
       <c r="E824" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F824" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G824" s="3"/>
+        <v>264</v>
+      </c>
+      <c r="G824" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H824" s="3">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I824" s="3">
         <v>65</v>
       </c>
       <c r="J824" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K824" s="3"/>
-      <c r="L824" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K824" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L824" s="3" t="s">
+        <v>2969</v>
+      </c>
       <c r="M824" s="3"/>
     </row>
     <row r="825" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A825" s="3" t="s">
-        <v>2966</v>
+        <v>2970</v>
       </c>
       <c r="B825" s="3" t="s">
-        <v>53</v>
+        <v>657</v>
       </c>
       <c r="C825" s="3" t="s">
-        <v>54</v>
+        <v>658</v>
       </c>
       <c r="D825" s="3" t="s">
-        <v>2967</v>
+        <v>2971</v>
       </c>
       <c r="E825" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F825" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G825" s="3"/>
+        <v>2582</v>
+      </c>
+      <c r="G825" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H825" s="3">
-        <v>61</v>
-      </c>
-      <c r="I825" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I825" s="3">
+        <v>65</v>
+      </c>
       <c r="J825" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K825" s="3"/>
-      <c r="L825" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K825" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L825" s="3" t="s">
+        <v>2972</v>
+      </c>
       <c r="M825" s="3"/>
     </row>
     <row r="826" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A826" s="3" t="s">
-        <v>2968</v>
+        <v>2973</v>
       </c>
       <c r="B826" s="3" t="s">
         <v>140</v>
@@ -41078,21 +41477,19 @@
         <v>141</v>
       </c>
       <c r="D826" s="3" t="s">
-        <v>2969</v>
+        <v>2974</v>
       </c>
       <c r="E826" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F826" s="3" t="s">
-        <v>1016</v>
+        <v>199</v>
       </c>
       <c r="G826" s="3"/>
       <c r="H826" s="3">
-        <v>53</v>
-      </c>
-      <c r="I826" s="3">
-        <v>65</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I826" s="3"/>
       <c r="J826" s="3" t="s">
         <v>70</v>
       </c>
@@ -41102,127 +41499,145 @@
     </row>
     <row r="827" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A827" s="3" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="B827" s="3" t="s">
-        <v>1563</v>
+        <v>187</v>
       </c>
       <c r="C827" s="3" t="s">
-        <v>1564</v>
+        <v>188</v>
       </c>
       <c r="D827" s="3" t="s">
-        <v>2971</v>
+        <v>2975</v>
       </c>
       <c r="E827" s="3" t="s">
-        <v>245</v>
+        <v>19</v>
       </c>
       <c r="F827" s="3" t="s">
-        <v>2972</v>
-      </c>
-      <c r="G827" s="3"/>
+        <v>2976</v>
+      </c>
+      <c r="G827" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H827" s="3">
-        <v>26</v>
-      </c>
-      <c r="I827" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="I827" s="3">
+        <v>65</v>
+      </c>
       <c r="J827" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K827" s="3"/>
-      <c r="L827" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K827" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L827" s="3" t="s">
+        <v>2977</v>
+      </c>
       <c r="M827" s="3"/>
     </row>
     <row r="828" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A828" s="3" t="s">
-        <v>2970</v>
+        <v>2907</v>
       </c>
       <c r="B828" s="3" t="s">
-        <v>1563</v>
+        <v>196</v>
       </c>
       <c r="C828" s="3" t="s">
-        <v>1564</v>
+        <v>197</v>
       </c>
       <c r="D828" s="3" t="s">
-        <v>2973</v>
+        <v>2978</v>
       </c>
       <c r="E828" s="3" t="s">
-        <v>245</v>
+        <v>19</v>
       </c>
       <c r="F828" s="3" t="s">
-        <v>2974</v>
-      </c>
-      <c r="G828" s="3"/>
+        <v>2979</v>
+      </c>
+      <c r="G828" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H828" s="3">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="I828" s="3">
         <v>65</v>
       </c>
       <c r="J828" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K828" s="3"/>
-      <c r="L828" s="3"/>
-      <c r="M828" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K828" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L828" s="3" t="s">
+        <v>2980</v>
+      </c>
+      <c r="M828" s="3" t="s">
+        <v>2981</v>
+      </c>
     </row>
     <row r="829" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A829" s="3" t="s">
-        <v>2970</v>
+        <v>2982</v>
       </c>
       <c r="B829" s="3" t="s">
-        <v>1563</v>
+        <v>72</v>
       </c>
       <c r="C829" s="3" t="s">
-        <v>1564</v>
+        <v>73</v>
       </c>
       <c r="D829" s="3" t="s">
-        <v>2975</v>
+        <v>2983</v>
       </c>
       <c r="E829" s="3" t="s">
-        <v>245</v>
+        <v>88</v>
       </c>
       <c r="F829" s="3" t="s">
-        <v>2972</v>
-      </c>
-      <c r="G829" s="3"/>
+        <v>2984</v>
+      </c>
+      <c r="G829" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H829" s="3">
-        <v>32</v>
-      </c>
-      <c r="I829" s="3">
-        <v>65</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="I829" s="3"/>
       <c r="J829" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K829" s="3"/>
-      <c r="L829" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K829" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L829" s="3" t="s">
+        <v>2985</v>
+      </c>
       <c r="M829" s="3"/>
     </row>
     <row r="830" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A830" s="3" t="s">
-        <v>2976</v>
+        <v>2986</v>
       </c>
       <c r="B830" s="3" t="s">
-        <v>1563</v>
+        <v>140</v>
       </c>
       <c r="C830" s="3" t="s">
-        <v>1564</v>
+        <v>141</v>
       </c>
       <c r="D830" s="3" t="s">
-        <v>2977</v>
+        <v>2987</v>
       </c>
       <c r="E830" s="3" t="s">
-        <v>245</v>
+        <v>68</v>
       </c>
       <c r="F830" s="3" t="s">
-        <v>2978</v>
+        <v>2988</v>
       </c>
       <c r="G830" s="3"/>
       <c r="H830" s="3">
-        <v>43</v>
-      </c>
-      <c r="I830" s="3">
-        <v>65</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="I830" s="3"/>
       <c r="J830" s="3" t="s">
         <v>70</v>
       </c>
@@ -41232,62 +41647,66 @@
     </row>
     <row r="831" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A831" s="3" t="s">
-        <v>2976</v>
+        <v>2989</v>
       </c>
       <c r="B831" s="3" t="s">
-        <v>1563</v>
+        <v>65</v>
       </c>
       <c r="C831" s="3" t="s">
-        <v>1564</v>
+        <v>66</v>
       </c>
       <c r="D831" s="3" t="s">
-        <v>2979</v>
+        <v>2990</v>
       </c>
       <c r="E831" s="3" t="s">
         <v>245</v>
       </c>
       <c r="F831" s="3" t="s">
-        <v>2980</v>
-      </c>
-      <c r="G831" s="3"/>
+        <v>1109</v>
+      </c>
+      <c r="G831" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H831" s="3">
-        <v>52</v>
-      </c>
-      <c r="I831" s="3">
-        <v>65</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I831" s="3"/>
       <c r="J831" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K831" s="3"/>
-      <c r="L831" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K831" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L831" s="3" t="s">
+        <v>2991</v>
+      </c>
       <c r="M831" s="3"/>
     </row>
     <row r="832" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A832" s="3" t="s">
-        <v>2976</v>
+        <v>2992</v>
       </c>
       <c r="B832" s="3" t="s">
-        <v>1563</v>
+        <v>140</v>
       </c>
       <c r="C832" s="3" t="s">
-        <v>1564</v>
+        <v>141</v>
       </c>
       <c r="D832" s="3" t="s">
-        <v>2981</v>
+        <v>2993</v>
       </c>
       <c r="E832" s="3" t="s">
-        <v>245</v>
+        <v>68</v>
       </c>
       <c r="F832" s="3" t="s">
-        <v>2982</v>
+        <v>1507</v>
       </c>
       <c r="G832" s="3"/>
       <c r="H832" s="3">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="I832" s="3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J832" s="3" t="s">
         <v>70</v>
@@ -41298,30 +41717,28 @@
     </row>
     <row r="833" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A833" s="3" t="s">
-        <v>2976</v>
+        <v>2994</v>
       </c>
       <c r="B833" s="3" t="s">
-        <v>1563</v>
+        <v>140</v>
       </c>
       <c r="C833" s="3" t="s">
-        <v>1564</v>
+        <v>141</v>
       </c>
       <c r="D833" s="3" t="s">
-        <v>2983</v>
+        <v>2995</v>
       </c>
       <c r="E833" s="3" t="s">
-        <v>245</v>
+        <v>68</v>
       </c>
       <c r="F833" s="3" t="s">
-        <v>2984</v>
+        <v>2996</v>
       </c>
       <c r="G833" s="3"/>
       <c r="H833" s="3">
-        <v>64</v>
-      </c>
-      <c r="I833" s="3">
-        <v>65</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I833" s="3"/>
       <c r="J833" s="3" t="s">
         <v>70</v>
       </c>
@@ -41331,26 +41748,26 @@
     </row>
     <row r="834" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A834" s="3" t="s">
-        <v>2976</v>
+        <v>2997</v>
       </c>
       <c r="B834" s="3" t="s">
-        <v>1563</v>
+        <v>140</v>
       </c>
       <c r="C834" s="3" t="s">
-        <v>1564</v>
+        <v>141</v>
       </c>
       <c r="D834" s="3" t="s">
-        <v>2985</v>
+        <v>2998</v>
       </c>
       <c r="E834" s="3" t="s">
-        <v>245</v>
+        <v>68</v>
       </c>
       <c r="F834" s="3" t="s">
-        <v>2986</v>
+        <v>289</v>
       </c>
       <c r="G834" s="3"/>
       <c r="H834" s="3">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="I834" s="3">
         <v>65</v>
@@ -41364,125 +41781,139 @@
     </row>
     <row r="835" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A835" s="3" t="s">
-        <v>2987</v>
+        <v>2999</v>
       </c>
       <c r="B835" s="3" t="s">
-        <v>1563</v>
+        <v>34</v>
       </c>
       <c r="C835" s="3" t="s">
-        <v>1564</v>
+        <v>35</v>
       </c>
       <c r="D835" s="3" t="s">
-        <v>2988</v>
+        <v>3000</v>
       </c>
       <c r="E835" s="3" t="s">
-        <v>245</v>
+        <v>19</v>
       </c>
       <c r="F835" s="3" t="s">
-        <v>2989</v>
-      </c>
-      <c r="G835" s="3"/>
+        <v>2748</v>
+      </c>
+      <c r="G835" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H835" s="3">
-        <v>67</v>
-      </c>
-      <c r="I835" s="3">
-        <v>65</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="I835" s="3"/>
       <c r="J835" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K835" s="3"/>
-      <c r="L835" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K835" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L835" s="3" t="s">
+        <v>3001</v>
+      </c>
       <c r="M835" s="3"/>
     </row>
     <row r="836" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A836" s="3" t="s">
-        <v>2990</v>
+        <v>3002</v>
       </c>
       <c r="B836" s="3" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C836" s="3" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="D836" s="3" t="s">
-        <v>2991</v>
+        <v>3003</v>
       </c>
       <c r="E836" s="3" t="s">
-        <v>19</v>
+        <v>306</v>
       </c>
       <c r="F836" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G836" s="3"/>
+        <v>257</v>
+      </c>
+      <c r="G836" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H836" s="3">
-        <v>62</v>
-      </c>
-      <c r="I836" s="3">
-        <v>65</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I836" s="3"/>
       <c r="J836" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K836" s="3"/>
-      <c r="L836" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K836" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L836" s="3" t="s">
+        <v>3004</v>
+      </c>
       <c r="M836" s="3"/>
     </row>
     <row r="837" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A837" s="3" t="s">
-        <v>2992</v>
+        <v>3005</v>
       </c>
       <c r="B837" s="3" t="s">
-        <v>657</v>
+        <v>59</v>
       </c>
       <c r="C837" s="3" t="s">
-        <v>658</v>
+        <v>60</v>
       </c>
       <c r="D837" s="3" t="s">
-        <v>2993</v>
+        <v>3006</v>
       </c>
       <c r="E837" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F837" s="3" t="s">
-        <v>2582</v>
-      </c>
-      <c r="G837" s="3"/>
+        <v>3007</v>
+      </c>
+      <c r="G837" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H837" s="3">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="I837" s="3">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J837" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K837" s="3"/>
-      <c r="L837" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K837" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L837" s="3" t="s">
+        <v>3008</v>
+      </c>
       <c r="M837" s="3"/>
     </row>
     <row r="838" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A838" s="3" t="s">
-        <v>2994</v>
+        <v>3009</v>
       </c>
       <c r="B838" s="3" t="s">
         <v>140</v>
       </c>
       <c r="C838" s="3" t="s">
-        <v>141</v>
+        <v>3010</v>
       </c>
       <c r="D838" s="3" t="s">
-        <v>2995</v>
+        <v>3011</v>
       </c>
       <c r="E838" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F838" s="3" t="s">
-        <v>199</v>
+        <v>1507</v>
       </c>
       <c r="G838" s="3"/>
       <c r="H838" s="3">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I838" s="3"/>
       <c r="J838" s="3" t="s">
@@ -41494,63 +41925,67 @@
     </row>
     <row r="839" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A839" s="3" t="s">
-        <v>2994</v>
+        <v>3012</v>
       </c>
       <c r="B839" s="3" t="s">
-        <v>187</v>
+        <v>2613</v>
       </c>
       <c r="C839" s="3" t="s">
-        <v>188</v>
+        <v>2614</v>
       </c>
       <c r="D839" s="3" t="s">
-        <v>2996</v>
+        <v>3013</v>
       </c>
       <c r="E839" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F839" s="3" t="s">
-        <v>2997</v>
-      </c>
-      <c r="G839" s="3"/>
+        <v>3014</v>
+      </c>
+      <c r="G839" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H839" s="3">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="I839" s="3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J839" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K839" s="3"/>
-      <c r="L839" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K839" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L839" s="3" t="s">
+        <v>3015</v>
+      </c>
       <c r="M839" s="3"/>
     </row>
     <row r="840" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A840" s="3" t="s">
-        <v>2907</v>
+        <v>3016</v>
       </c>
       <c r="B840" s="3" t="s">
-        <v>196</v>
+        <v>140</v>
       </c>
       <c r="C840" s="3" t="s">
-        <v>197</v>
+        <v>3010</v>
       </c>
       <c r="D840" s="3" t="s">
-        <v>2998</v>
+        <v>3017</v>
       </c>
       <c r="E840" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F840" s="3" t="s">
-        <v>2999</v>
+        <v>1694</v>
       </c>
       <c r="G840" s="3"/>
       <c r="H840" s="3">
-        <v>74</v>
-      </c>
-      <c r="I840" s="3">
-        <v>65</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="I840" s="3"/>
       <c r="J840" s="3" t="s">
         <v>70</v>
       </c>
@@ -41560,123 +41995,141 @@
     </row>
     <row r="841" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A841" s="3" t="s">
-        <v>3000</v>
+        <v>3018</v>
       </c>
       <c r="B841" s="3" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="C841" s="3" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="D841" s="3" t="s">
-        <v>3001</v>
+        <v>3019</v>
       </c>
       <c r="E841" s="3" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="F841" s="3" t="s">
-        <v>3002</v>
-      </c>
-      <c r="G841" s="3"/>
+        <v>397</v>
+      </c>
+      <c r="G841" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H841" s="3">
-        <v>44</v>
-      </c>
-      <c r="I841" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="I841" s="3">
+        <v>65</v>
+      </c>
       <c r="J841" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K841" s="3"/>
-      <c r="L841" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K841" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L841" s="3" t="s">
+        <v>3020</v>
+      </c>
       <c r="M841" s="3"/>
     </row>
     <row r="842" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A842" s="3" t="s">
-        <v>3003</v>
+        <v>3021</v>
       </c>
       <c r="B842" s="3" t="s">
-        <v>72</v>
+        <v>2613</v>
       </c>
       <c r="C842" s="3" t="s">
-        <v>73</v>
+        <v>2614</v>
       </c>
       <c r="D842" s="3" t="s">
-        <v>3004</v>
+        <v>3022</v>
       </c>
       <c r="E842" s="3" t="s">
-        <v>88</v>
+        <v>245</v>
       </c>
       <c r="F842" s="3" t="s">
-        <v>3005</v>
-      </c>
-      <c r="G842" s="3"/>
+        <v>3023</v>
+      </c>
+      <c r="G842" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H842" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="I842" s="3"/>
       <c r="J842" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K842" s="3"/>
-      <c r="L842" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K842" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L842" s="3" t="s">
+        <v>3024</v>
+      </c>
       <c r="M842" s="3"/>
     </row>
     <row r="843" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A843" s="3" t="s">
-        <v>3006</v>
+        <v>3025</v>
       </c>
       <c r="B843" s="3" t="s">
-        <v>657</v>
+        <v>196</v>
       </c>
       <c r="C843" s="3" t="s">
-        <v>658</v>
+        <v>197</v>
       </c>
       <c r="D843" s="3" t="s">
-        <v>3007</v>
+        <v>3026</v>
       </c>
       <c r="E843" s="3" t="s">
-        <v>19</v>
+        <v>306</v>
       </c>
       <c r="F843" s="3" t="s">
-        <v>2063</v>
-      </c>
-      <c r="G843" s="3"/>
-      <c r="H843" s="3">
-        <v>58</v>
-      </c>
+        <v>2453</v>
+      </c>
+      <c r="G843" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H843" s="3"/>
       <c r="I843" s="3"/>
       <c r="J843" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K843" s="3"/>
-      <c r="L843" s="3"/>
-      <c r="M843" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K843" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L843" s="3" t="s">
+        <v>3027</v>
+      </c>
+      <c r="M843" s="3" t="s">
+        <v>3028</v>
+      </c>
     </row>
     <row r="844" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A844" s="3" t="s">
-        <v>3008</v>
+        <v>3029</v>
       </c>
       <c r="B844" s="3" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="C844" s="3" t="s">
-        <v>73</v>
+        <v>3010</v>
       </c>
       <c r="D844" s="3" t="s">
-        <v>3009</v>
+        <v>3030</v>
       </c>
       <c r="E844" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F844" s="3" t="s">
-        <v>3010</v>
+        <v>3031</v>
       </c>
       <c r="G844" s="3"/>
       <c r="H844" s="3">
-        <v>63</v>
-      </c>
-      <c r="I844" s="3">
-        <v>65</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I844" s="3"/>
       <c r="J844" s="3" t="s">
         <v>70</v>
       </c>
@@ -41686,30 +42139,26 @@
     </row>
     <row r="845" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A845" s="3" t="s">
-        <v>3011</v>
+        <v>3032</v>
       </c>
       <c r="B845" s="3" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="C845" s="3" t="s">
-        <v>73</v>
+        <v>3010</v>
       </c>
       <c r="D845" s="3" t="s">
-        <v>3012</v>
+        <v>3033</v>
       </c>
       <c r="E845" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F845" s="3" t="s">
-        <v>1483</v>
+        <v>2392</v>
       </c>
       <c r="G845" s="3"/>
-      <c r="H845" s="3">
-        <v>60</v>
-      </c>
-      <c r="I845" s="3">
-        <v>65</v>
-      </c>
+      <c r="H845" s="3"/>
+      <c r="I845" s="3"/>
       <c r="J845" s="3" t="s">
         <v>70</v>
       </c>
@@ -41719,106 +42168,122 @@
     </row>
     <row r="846" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A846" s="3" t="s">
-        <v>3013</v>
+        <v>3034</v>
       </c>
       <c r="B846" s="3" t="s">
-        <v>196</v>
+        <v>390</v>
       </c>
       <c r="C846" s="3" t="s">
-        <v>197</v>
+        <v>2776</v>
       </c>
       <c r="D846" s="3" t="s">
-        <v>3014</v>
+        <v>3035</v>
       </c>
       <c r="E846" s="3" t="s">
-        <v>19</v>
+        <v>306</v>
       </c>
       <c r="F846" s="3" t="s">
-        <v>3015</v>
-      </c>
-      <c r="G846" s="3"/>
+        <v>1941</v>
+      </c>
+      <c r="G846" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H846" s="3">
-        <v>55</v>
-      </c>
-      <c r="I846" s="3">
-        <v>65</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I846" s="3"/>
       <c r="J846" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K846" s="3"/>
-      <c r="L846" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K846" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L846" s="3" t="s">
+        <v>3036</v>
+      </c>
       <c r="M846" s="3"/>
     </row>
     <row r="847" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A847" s="3" t="s">
-        <v>3016</v>
+        <v>3037</v>
       </c>
       <c r="B847" s="3" t="s">
-        <v>53</v>
+        <v>390</v>
       </c>
       <c r="C847" s="3" t="s">
-        <v>54</v>
+        <v>2776</v>
       </c>
       <c r="D847" s="3" t="s">
-        <v>3017</v>
+        <v>3038</v>
       </c>
       <c r="E847" s="3" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="F847" s="3" t="s">
-        <v>1520</v>
-      </c>
-      <c r="G847" s="3"/>
+        <v>3039</v>
+      </c>
+      <c r="G847" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H847" s="3">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="I847" s="3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="J847" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K847" s="3"/>
-      <c r="L847" s="3"/>
-      <c r="M847" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K847" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L847" s="3" t="s">
+        <v>3040</v>
+      </c>
+      <c r="M847" s="3" t="s">
+        <v>3041</v>
+      </c>
     </row>
     <row r="848" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A848" s="3" t="s">
-        <v>3018</v>
+        <v>3042</v>
       </c>
       <c r="B848" s="3" t="s">
-        <v>196</v>
+        <v>34</v>
       </c>
       <c r="C848" s="3" t="s">
-        <v>197</v>
+        <v>35</v>
       </c>
       <c r="D848" s="3" t="s">
-        <v>3019</v>
+        <v>3043</v>
       </c>
       <c r="E848" s="3" t="s">
-        <v>19</v>
+        <v>306</v>
       </c>
       <c r="F848" s="3" t="s">
-        <v>3020</v>
-      </c>
-      <c r="G848" s="3"/>
+        <v>803</v>
+      </c>
+      <c r="G848" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H848" s="3">
-        <v>63</v>
-      </c>
-      <c r="I848" s="3">
-        <v>65</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I848" s="3"/>
       <c r="J848" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K848" s="3"/>
-      <c r="L848" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K848" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L848" s="3" t="s">
+        <v>3044</v>
+      </c>
       <c r="M848" s="3"/>
     </row>
     <row r="849" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A849" s="3" t="s">
-        <v>3021</v>
+        <v>3045</v>
       </c>
       <c r="B849" s="3" t="s">
         <v>196</v>
@@ -41827,50 +42292,56 @@
         <v>197</v>
       </c>
       <c r="D849" s="3" t="s">
-        <v>3022</v>
+        <v>3046</v>
       </c>
       <c r="E849" s="3" t="s">
-        <v>19</v>
+        <v>306</v>
       </c>
       <c r="F849" s="3" t="s">
-        <v>3023</v>
-      </c>
-      <c r="G849" s="3"/>
+        <v>3047</v>
+      </c>
+      <c r="G849" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H849" s="3">
-        <v>62</v>
-      </c>
-      <c r="I849" s="3">
-        <v>65</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I849" s="3"/>
       <c r="J849" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K849" s="3"/>
-      <c r="L849" s="3"/>
-      <c r="M849" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K849" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L849" s="3" t="s">
+        <v>3048</v>
+      </c>
+      <c r="M849" s="3" t="s">
+        <v>3049</v>
+      </c>
     </row>
     <row r="850" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A850" s="3" t="s">
-        <v>3024</v>
+        <v>3050</v>
       </c>
       <c r="B850" s="3" t="s">
         <v>140</v>
       </c>
       <c r="C850" s="3" t="s">
-        <v>141</v>
+        <v>3010</v>
       </c>
       <c r="D850" s="3" t="s">
-        <v>3025</v>
+        <v>3051</v>
       </c>
       <c r="E850" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F850" s="3" t="s">
-        <v>3026</v>
+        <v>3052</v>
       </c>
       <c r="G850" s="3"/>
       <c r="H850" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I850" s="3"/>
       <c r="J850" s="3" t="s">
@@ -41882,30 +42353,28 @@
     </row>
     <row r="851" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A851" s="3" t="s">
-        <v>3027</v>
+        <v>3053</v>
       </c>
       <c r="B851" s="3" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="C851" s="3" t="s">
-        <v>188</v>
+        <v>3010</v>
       </c>
       <c r="D851" s="3" t="s">
-        <v>3028</v>
+        <v>3054</v>
       </c>
       <c r="E851" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F851" s="3" t="s">
-        <v>3029</v>
+        <v>3055</v>
       </c>
       <c r="G851" s="3"/>
       <c r="H851" s="3">
-        <v>55</v>
-      </c>
-      <c r="I851" s="3">
-        <v>55</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="I851" s="3"/>
       <c r="J851" s="3" t="s">
         <v>70</v>
       </c>
@@ -41915,26 +42384,26 @@
     </row>
     <row r="852" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A852" s="3" t="s">
-        <v>3030</v>
+        <v>3056</v>
       </c>
       <c r="B852" s="3" t="s">
-        <v>2613</v>
+        <v>657</v>
       </c>
       <c r="C852" s="3" t="s">
-        <v>2614</v>
+        <v>658</v>
       </c>
       <c r="D852" s="3" t="s">
-        <v>3031</v>
+        <v>3057</v>
       </c>
       <c r="E852" s="3" t="s">
-        <v>306</v>
+        <v>68</v>
       </c>
       <c r="F852" s="3" t="s">
-        <v>3032</v>
+        <v>3058</v>
       </c>
       <c r="G852" s="3"/>
       <c r="H852" s="3">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I852" s="3"/>
       <c r="J852" s="3" t="s">
@@ -41946,123 +42415,147 @@
     </row>
     <row r="853" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A853" s="3" t="s">
-        <v>3033</v>
+        <v>3059</v>
       </c>
       <c r="B853" s="3" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="C853" s="3" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D853" s="3" t="s">
-        <v>3034</v>
+        <v>3060</v>
       </c>
       <c r="E853" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F853" s="3" t="s">
-        <v>2824</v>
-      </c>
-      <c r="G853" s="3"/>
+        <v>3061</v>
+      </c>
+      <c r="G853" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H853" s="3">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="I853" s="3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="J853" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K853" s="3"/>
-      <c r="L853" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K853" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L853" s="3" t="s">
+        <v>3062</v>
+      </c>
       <c r="M853" s="3"/>
     </row>
     <row r="854" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A854" s="3" t="s">
-        <v>3035</v>
+        <v>3063</v>
       </c>
       <c r="B854" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C854" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D854" s="3" t="s">
-        <v>3036</v>
+        <v>3064</v>
       </c>
       <c r="E854" s="3" t="s">
-        <v>245</v>
+        <v>19</v>
       </c>
       <c r="F854" s="3" t="s">
-        <v>1109</v>
-      </c>
-      <c r="G854" s="3"/>
+        <v>3065</v>
+      </c>
+      <c r="G854" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H854" s="3">
-        <v>34</v>
-      </c>
-      <c r="I854" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="I854" s="3">
+        <v>55</v>
+      </c>
       <c r="J854" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K854" s="3"/>
-      <c r="L854" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K854" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L854" s="3" t="s">
+        <v>3066</v>
+      </c>
       <c r="M854" s="3"/>
     </row>
     <row r="855" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A855" s="3" t="s">
-        <v>3037</v>
+        <v>3067</v>
       </c>
       <c r="B855" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C855" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D855" s="3" t="s">
-        <v>3038</v>
+        <v>3068</v>
       </c>
       <c r="E855" s="3" t="s">
-        <v>245</v>
+        <v>19</v>
       </c>
       <c r="F855" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="G855" s="3"/>
+        <v>1388</v>
+      </c>
+      <c r="G855" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H855" s="3">
-        <v>34</v>
-      </c>
-      <c r="I855" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I855" s="3">
+        <v>55</v>
+      </c>
       <c r="J855" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K855" s="3"/>
-      <c r="L855" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K855" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L855" s="3" t="s">
+        <v>3069</v>
+      </c>
       <c r="M855" s="3"/>
     </row>
     <row r="856" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A856" s="3" t="s">
-        <v>3039</v>
+        <v>3070</v>
       </c>
       <c r="B856" s="3" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="C856" s="3" t="s">
-        <v>66</v>
+        <v>3010</v>
       </c>
       <c r="D856" s="3" t="s">
-        <v>3040</v>
+        <v>3071</v>
       </c>
       <c r="E856" s="3" t="s">
-        <v>245</v>
+        <v>68</v>
       </c>
       <c r="F856" s="3" t="s">
-        <v>490</v>
+        <v>711</v>
       </c>
       <c r="G856" s="3"/>
       <c r="H856" s="3">
-        <v>21</v>
-      </c>
-      <c r="I856" s="3"/>
+        <v>44</v>
+      </c>
+      <c r="I856" s="3">
+        <v>40</v>
+      </c>
       <c r="J856" s="3" t="s">
         <v>70</v>
       </c>
@@ -42072,26 +42565,26 @@
     </row>
     <row r="857" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A857" s="3" t="s">
-        <v>3039</v>
+        <v>3072</v>
       </c>
       <c r="B857" s="3" t="s">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="C857" s="3" t="s">
-        <v>66</v>
+        <v>3010</v>
       </c>
       <c r="D857" s="3" t="s">
-        <v>3041</v>
+        <v>3073</v>
       </c>
       <c r="E857" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="F857" s="3" t="s">
-        <v>3042</v>
+        <v>3055</v>
       </c>
       <c r="G857" s="3"/>
       <c r="H857" s="3">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="I857" s="3"/>
       <c r="J857" s="3" t="s">
@@ -42103,57 +42596,65 @@
     </row>
     <row r="858" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A858" s="3" t="s">
-        <v>3043</v>
+        <v>3074</v>
       </c>
       <c r="B858" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C858" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D858" s="3" t="s">
+        <v>3075</v>
+      </c>
+      <c r="E858" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F858" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G858" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H858" s="3">
+        <v>68</v>
+      </c>
+      <c r="I858" s="3">
         <v>65</v>
       </c>
-      <c r="C858" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D858" s="3" t="s">
-        <v>3044</v>
-      </c>
-      <c r="E858" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F858" s="3" t="s">
-        <v>2313</v>
-      </c>
-      <c r="G858" s="3"/>
-      <c r="H858" s="3">
-        <v>35</v>
-      </c>
-      <c r="I858" s="3"/>
       <c r="J858" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K858" s="3"/>
-      <c r="L858" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K858" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L858" s="3" t="s">
+        <v>3076</v>
+      </c>
       <c r="M858" s="3"/>
     </row>
     <row r="859" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A859" s="3" t="s">
-        <v>3043</v>
+        <v>3077</v>
       </c>
       <c r="B859" s="3" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="C859" s="3" t="s">
-        <v>60</v>
+        <v>3010</v>
       </c>
       <c r="D859" s="3" t="s">
-        <v>3045</v>
+        <v>3078</v>
       </c>
       <c r="E859" s="3" t="s">
-        <v>306</v>
+        <v>68</v>
       </c>
       <c r="F859" s="3" t="s">
-        <v>3046</v>
+        <v>490</v>
       </c>
       <c r="G859" s="3"/>
       <c r="H859" s="3">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I859" s="3"/>
       <c r="J859" s="3" t="s">
@@ -42165,7 +42666,7 @@
     </row>
     <row r="860" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A860" s="3" t="s">
-        <v>3047</v>
+        <v>3079</v>
       </c>
       <c r="B860" s="3" t="s">
         <v>65</v>
@@ -42174,20 +42675,20 @@
         <v>66</v>
       </c>
       <c r="D860" s="3" t="s">
-        <v>3048</v>
+        <v>3080</v>
       </c>
       <c r="E860" s="3" t="s">
-        <v>2016</v>
+        <v>68</v>
       </c>
       <c r="F860" s="3" t="s">
-        <v>732</v>
+        <v>3081</v>
       </c>
       <c r="G860" s="3"/>
       <c r="H860" s="3">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="I860" s="3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J860" s="3" t="s">
         <v>70</v>
@@ -42198,91 +42699,107 @@
     </row>
     <row r="861" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A861" s="3" t="s">
-        <v>3049</v>
+        <v>3082</v>
       </c>
       <c r="B861" s="3" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="C861" s="3" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="D861" s="3" t="s">
-        <v>3050</v>
+        <v>3083</v>
       </c>
       <c r="E861" s="3" t="s">
-        <v>2016</v>
+        <v>19</v>
       </c>
       <c r="F861" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="G861" s="3"/>
+        <v>3084</v>
+      </c>
+      <c r="G861" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H861" s="3">
-        <v>50</v>
-      </c>
-      <c r="I861" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="I861" s="3">
+        <v>55</v>
+      </c>
       <c r="J861" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K861" s="3"/>
-      <c r="L861" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K861" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L861" s="3" t="s">
+        <v>3085</v>
+      </c>
       <c r="M861" s="3"/>
     </row>
     <row r="862" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A862" s="3" t="s">
-        <v>3051</v>
+        <v>3086</v>
       </c>
       <c r="B862" s="3" t="s">
-        <v>667</v>
+        <v>2613</v>
       </c>
       <c r="C862" s="3" t="s">
-        <v>668</v>
+        <v>2614</v>
       </c>
       <c r="D862" s="3" t="s">
-        <v>3052</v>
+        <v>3087</v>
       </c>
       <c r="E862" s="3" t="s">
-        <v>2016</v>
+        <v>19</v>
       </c>
       <c r="F862" s="3" t="s">
-        <v>3053</v>
-      </c>
-      <c r="G862" s="3"/>
+        <v>285</v>
+      </c>
+      <c r="G862" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H862" s="3">
-        <v>38</v>
-      </c>
-      <c r="I862" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="I862" s="3">
+        <v>60</v>
+      </c>
       <c r="J862" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K862" s="3"/>
-      <c r="L862" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K862" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L862" s="3" t="s">
+        <v>3088</v>
+      </c>
       <c r="M862" s="3"/>
     </row>
     <row r="863" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A863" s="3" t="s">
-        <v>3054</v>
+        <v>3089</v>
       </c>
       <c r="B863" s="3" t="s">
         <v>140</v>
       </c>
       <c r="C863" s="3" t="s">
-        <v>141</v>
+        <v>3010</v>
       </c>
       <c r="D863" s="3" t="s">
-        <v>3055</v>
+        <v>3090</v>
       </c>
       <c r="E863" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F863" s="3" t="s">
-        <v>1507</v>
+        <v>995</v>
       </c>
       <c r="G863" s="3"/>
       <c r="H863" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I863" s="3">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="J863" s="3" t="s">
         <v>70</v>
@@ -42293,29 +42810,29 @@
     </row>
     <row r="864" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A864" s="3" t="s">
-        <v>3056</v>
+        <v>3091</v>
       </c>
       <c r="B864" s="3" t="s">
-        <v>196</v>
+        <v>65</v>
       </c>
       <c r="C864" s="3" t="s">
-        <v>197</v>
+        <v>66</v>
       </c>
       <c r="D864" s="3" t="s">
-        <v>3057</v>
+        <v>3092</v>
       </c>
       <c r="E864" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F864" s="3" t="s">
-        <v>1242</v>
+        <v>2945</v>
       </c>
       <c r="G864" s="3"/>
       <c r="H864" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I864" s="3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J864" s="3" t="s">
         <v>70</v>
@@ -42326,29 +42843,29 @@
     </row>
     <row r="865" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A865" s="3" t="s">
-        <v>3058</v>
+        <v>3093</v>
       </c>
       <c r="B865" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C865" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D865" s="3" t="s">
-        <v>3059</v>
+        <v>3094</v>
       </c>
       <c r="E865" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F865" s="3" t="s">
-        <v>3060</v>
+        <v>3095</v>
       </c>
       <c r="G865" s="3"/>
       <c r="H865" s="3">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I865" s="3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J865" s="3" t="s">
         <v>70</v>
@@ -42359,104 +42876,122 @@
     </row>
     <row r="866" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A866" s="3" t="s">
-        <v>3061</v>
+        <v>3096</v>
       </c>
       <c r="B866" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C866" s="3" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D866" s="3" t="s">
-        <v>3062</v>
+        <v>3097</v>
       </c>
       <c r="E866" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F866" s="3" t="s">
-        <v>1344</v>
-      </c>
-      <c r="G866" s="3"/>
+        <v>1396</v>
+      </c>
+      <c r="G866" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H866" s="3">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="I866" s="3">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="J866" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K866" s="3"/>
-      <c r="L866" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K866" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L866" s="3" t="s">
+        <v>3098</v>
+      </c>
       <c r="M866" s="3"/>
     </row>
     <row r="867" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A867" s="3" t="s">
-        <v>3063</v>
+        <v>3099</v>
       </c>
       <c r="B867" s="3" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="C867" s="3" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
       <c r="D867" s="3" t="s">
-        <v>3064</v>
+        <v>3100</v>
       </c>
       <c r="E867" s="3" t="s">
-        <v>68</v>
+        <v>306</v>
       </c>
       <c r="F867" s="3" t="s">
-        <v>3065</v>
-      </c>
-      <c r="G867" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="G867" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H867" s="3">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I867" s="3"/>
       <c r="J867" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K867" s="3"/>
-      <c r="L867" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K867" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L867" s="3" t="s">
+        <v>3101</v>
+      </c>
       <c r="M867" s="3"/>
     </row>
     <row r="868" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A868" s="3" t="s">
-        <v>3066</v>
+        <v>3102</v>
       </c>
       <c r="B868" s="3" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="C868" s="3" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D868" s="3" t="s">
-        <v>3067</v>
+        <v>3103</v>
       </c>
       <c r="E868" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F868" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G868" s="3"/>
+        <v>216</v>
+      </c>
+      <c r="G868" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H868" s="3">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="I868" s="3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J868" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K868" s="3"/>
-      <c r="L868" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K868" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L868" s="3" t="s">
+        <v>3104</v>
+      </c>
       <c r="M868" s="3"/>
     </row>
     <row r="869" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A869" s="3" t="s">
-        <v>3068</v>
+        <v>3105</v>
       </c>
       <c r="B869" s="3" t="s">
         <v>72</v>
@@ -42465,87 +43000,95 @@
         <v>73</v>
       </c>
       <c r="D869" s="3" t="s">
-        <v>3069</v>
+        <v>3106</v>
       </c>
       <c r="E869" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F869" s="3" t="s">
-        <v>3070</v>
-      </c>
-      <c r="G869" s="3"/>
+        <v>963</v>
+      </c>
+      <c r="G869" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H869" s="3">
-        <v>65</v>
-      </c>
-      <c r="I869" s="3">
-        <v>70</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="I869" s="3"/>
       <c r="J869" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K869" s="3"/>
-      <c r="L869" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K869" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L869" s="3" t="s">
+        <v>3107</v>
+      </c>
       <c r="M869" s="3"/>
     </row>
     <row r="870" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A870" s="3" t="s">
-        <v>3071</v>
+        <v>3108</v>
       </c>
       <c r="B870" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="C870" s="3" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="D870" s="3" t="s">
-        <v>3072</v>
+        <v>3109</v>
       </c>
       <c r="E870" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F870" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G870" s="3"/>
+        <v>2471</v>
+      </c>
+      <c r="G870" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H870" s="3">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="I870" s="3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J870" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K870" s="3"/>
-      <c r="L870" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K870" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L870" s="3" t="s">
+        <v>3110</v>
+      </c>
       <c r="M870" s="3"/>
     </row>
     <row r="871" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A871" s="3" t="s">
-        <v>3073</v>
+        <v>3111</v>
       </c>
       <c r="B871" s="3" t="s">
         <v>140</v>
       </c>
       <c r="C871" s="3" t="s">
-        <v>141</v>
+        <v>3010</v>
       </c>
       <c r="D871" s="3" t="s">
-        <v>3074</v>
+        <v>3112</v>
       </c>
       <c r="E871" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F871" s="3" t="s">
-        <v>289</v>
+        <v>2169</v>
       </c>
       <c r="G871" s="3"/>
       <c r="H871" s="3">
-        <v>75</v>
-      </c>
-      <c r="I871" s="3">
-        <v>65</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="I871" s="3"/>
       <c r="J871" s="3" t="s">
         <v>70</v>
       </c>
@@ -42555,62 +43098,68 @@
     </row>
     <row r="872" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A872" s="3" t="s">
-        <v>3075</v>
+        <v>3113</v>
       </c>
       <c r="B872" s="3" t="s">
-        <v>196</v>
+        <v>2613</v>
       </c>
       <c r="C872" s="3" t="s">
-        <v>197</v>
+        <v>2614</v>
       </c>
       <c r="D872" s="3" t="s">
-        <v>3076</v>
+        <v>3114</v>
       </c>
       <c r="E872" s="3" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="F872" s="3" t="s">
-        <v>3077</v>
-      </c>
-      <c r="G872" s="3"/>
+        <v>3115</v>
+      </c>
+      <c r="G872" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H872" s="3">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="I872" s="3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J872" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K872" s="3"/>
-      <c r="L872" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K872" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L872" s="3" t="s">
+        <v>3116</v>
+      </c>
       <c r="M872" s="3"/>
     </row>
     <row r="873" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A873" s="3" t="s">
-        <v>3078</v>
+        <v>3117</v>
       </c>
       <c r="B873" s="3" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="C873" s="3" t="s">
-        <v>79</v>
+        <v>3010</v>
       </c>
       <c r="D873" s="3" t="s">
-        <v>3079</v>
+        <v>3118</v>
       </c>
       <c r="E873" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="F873" s="3" t="s">
-        <v>3080</v>
+        <v>27</v>
       </c>
       <c r="G873" s="3"/>
       <c r="H873" s="3">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="I873" s="3">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="J873" s="3" t="s">
         <v>70</v>
@@ -42621,57 +43170,65 @@
     </row>
     <row r="874" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A874" s="3" t="s">
-        <v>3081</v>
+        <v>3119</v>
       </c>
       <c r="B874" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C874" s="3" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D874" s="3" t="s">
-        <v>3082</v>
+        <v>3120</v>
       </c>
       <c r="E874" s="3" t="s">
-        <v>2016</v>
+        <v>19</v>
       </c>
       <c r="F874" s="3" t="s">
-        <v>3083</v>
-      </c>
-      <c r="G874" s="3"/>
+        <v>3121</v>
+      </c>
+      <c r="G874" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H874" s="3">
-        <v>24</v>
-      </c>
-      <c r="I874" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="I874" s="3">
+        <v>45</v>
+      </c>
       <c r="J874" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K874" s="3"/>
-      <c r="L874" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K874" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L874" s="3" t="s">
+        <v>3122</v>
+      </c>
       <c r="M874" s="3"/>
     </row>
     <row r="875" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A875" s="3" t="s">
-        <v>3084</v>
+        <v>3123</v>
       </c>
       <c r="B875" s="3" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="C875" s="3" t="s">
-        <v>35</v>
+        <v>3010</v>
       </c>
       <c r="D875" s="3" t="s">
-        <v>3085</v>
+        <v>3124</v>
       </c>
       <c r="E875" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F875" s="3" t="s">
-        <v>2748</v>
+        <v>3125</v>
       </c>
       <c r="G875" s="3"/>
       <c r="H875" s="3">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I875" s="3"/>
       <c r="J875" s="3" t="s">
@@ -42683,96 +43240,106 @@
     </row>
     <row r="876" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A876" s="3" t="s">
-        <v>3086</v>
+        <v>3126</v>
       </c>
       <c r="B876" s="3" t="s">
-        <v>34</v>
+        <v>2613</v>
       </c>
       <c r="C876" s="3" t="s">
-        <v>35</v>
+        <v>2614</v>
       </c>
       <c r="D876" s="3" t="s">
-        <v>3087</v>
+        <v>3127</v>
       </c>
       <c r="E876" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F876" s="3" t="s">
-        <v>3088</v>
-      </c>
-      <c r="G876" s="3"/>
+        <v>3128</v>
+      </c>
+      <c r="G876" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H876" s="3">
+        <v>70</v>
+      </c>
+      <c r="I876" s="3">
         <v>65</v>
       </c>
-      <c r="I876" s="3">
-        <v>55</v>
-      </c>
       <c r="J876" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K876" s="3"/>
-      <c r="L876" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K876" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L876" s="3" t="s">
+        <v>3129</v>
+      </c>
       <c r="M876" s="3"/>
     </row>
     <row r="877" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A877" s="3" t="s">
-        <v>3089</v>
+        <v>3130</v>
       </c>
       <c r="B877" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C877" s="3" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D877" s="3" t="s">
-        <v>3090</v>
+        <v>3131</v>
       </c>
       <c r="E877" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F877" s="3" t="s">
-        <v>3091</v>
-      </c>
-      <c r="G877" s="3"/>
+        <v>3132</v>
+      </c>
+      <c r="G877" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H877" s="3">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="I877" s="3">
         <v>60</v>
       </c>
       <c r="J877" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K877" s="3"/>
-      <c r="L877" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K877" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L877" s="3" t="s">
+        <v>3133</v>
+      </c>
       <c r="M877" s="3"/>
     </row>
     <row r="878" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A878" s="3" t="s">
-        <v>3092</v>
+        <v>3134</v>
       </c>
       <c r="B878" s="3" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="C878" s="3" t="s">
-        <v>188</v>
+        <v>3010</v>
       </c>
       <c r="D878" s="3" t="s">
-        <v>3093</v>
+        <v>3135</v>
       </c>
       <c r="E878" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F878" s="3" t="s">
-        <v>3094</v>
+        <v>3136</v>
       </c>
       <c r="G878" s="3"/>
       <c r="H878" s="3">
-        <v>48</v>
-      </c>
-      <c r="I878" s="3">
-        <v>60</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="I878" s="3"/>
       <c r="J878" s="3" t="s">
         <v>70</v>
       </c>
@@ -42782,92 +43349,102 @@
     </row>
     <row r="879" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A879" s="3" t="s">
-        <v>3095</v>
+        <v>3137</v>
       </c>
       <c r="B879" s="3" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="C879" s="3" t="s">
-        <v>79</v>
+        <v>3010</v>
       </c>
       <c r="D879" s="3" t="s">
-        <v>3096</v>
+        <v>3138</v>
       </c>
       <c r="E879" s="3" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="F879" s="3" t="s">
-        <v>3097</v>
-      </c>
-      <c r="G879" s="3"/>
+        <v>3139</v>
+      </c>
+      <c r="G879" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H879" s="3">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="I879" s="3">
         <v>65</v>
       </c>
       <c r="J879" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K879" s="3"/>
-      <c r="L879" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K879" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L879" s="3" t="s">
+        <v>3140</v>
+      </c>
       <c r="M879" s="3"/>
     </row>
     <row r="880" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A880" s="3" t="s">
-        <v>3098</v>
+        <v>3141</v>
       </c>
       <c r="B880" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C880" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D880" s="3" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E880" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F880" s="3" t="s">
+        <v>3143</v>
+      </c>
+      <c r="G880" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H880" s="3">
         <v>53</v>
       </c>
-      <c r="C880" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D880" s="3" t="s">
-        <v>3099</v>
-      </c>
-      <c r="E880" s="3" t="s">
-        <v>2016</v>
-      </c>
-      <c r="F880" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G880" s="3"/>
-      <c r="H880" s="3">
-        <v>8</v>
-      </c>
-      <c r="I880" s="3">
-        <v>65</v>
-      </c>
+      <c r="I880" s="3"/>
       <c r="J880" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K880" s="3"/>
-      <c r="L880" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K880" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L880" s="3" t="s">
+        <v>3144</v>
+      </c>
       <c r="M880" s="3"/>
     </row>
     <row r="881" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A881" s="3" t="s">
-        <v>3098</v>
+        <v>3145</v>
       </c>
       <c r="B881" s="3" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="C881" s="3" t="s">
-        <v>73</v>
+        <v>3010</v>
       </c>
       <c r="D881" s="3" t="s">
-        <v>3100</v>
+        <v>3146</v>
       </c>
       <c r="E881" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F881" s="3" t="s">
-        <v>1569</v>
+        <v>170</v>
       </c>
       <c r="G881" s="3"/>
       <c r="H881" s="3">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I881" s="3">
         <v>65</v>
@@ -42881,29 +43458,29 @@
     </row>
     <row r="882" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A882" s="3" t="s">
-        <v>3101</v>
+        <v>3147</v>
       </c>
       <c r="B882" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C882" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D882" s="3" t="s">
-        <v>3102</v>
+        <v>3148</v>
       </c>
       <c r="E882" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F882" s="3" t="s">
-        <v>3103</v>
+        <v>3149</v>
       </c>
       <c r="G882" s="3"/>
       <c r="H882" s="3">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="I882" s="3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J882" s="3" t="s">
         <v>70</v>
@@ -42914,7 +43491,7 @@
     </row>
     <row r="883" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A883" s="3" t="s">
-        <v>3104</v>
+        <v>3150</v>
       </c>
       <c r="B883" s="3" t="s">
         <v>72</v>
@@ -42923,53 +43500,59 @@
         <v>73</v>
       </c>
       <c r="D883" s="3" t="s">
-        <v>3105</v>
+        <v>3151</v>
       </c>
       <c r="E883" s="3" t="s">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="F883" s="3" t="s">
-        <v>3106</v>
-      </c>
-      <c r="G883" s="3"/>
+        <v>860</v>
+      </c>
+      <c r="G883" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H883" s="3">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="I883" s="3">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J883" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K883" s="3"/>
-      <c r="L883" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K883" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L883" s="3" t="s">
+        <v>3152</v>
+      </c>
       <c r="M883" s="3"/>
     </row>
     <row r="884" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A884" s="3" t="s">
-        <v>3107</v>
+        <v>3153</v>
       </c>
       <c r="B884" s="3" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="C884" s="3" t="s">
-        <v>79</v>
+        <v>3010</v>
       </c>
       <c r="D884" s="3" t="s">
-        <v>3108</v>
+        <v>3154</v>
       </c>
       <c r="E884" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F884" s="3" t="s">
-        <v>3109</v>
+        <v>3155</v>
       </c>
       <c r="G884" s="3"/>
       <c r="H884" s="3">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="I884" s="3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J884" s="3" t="s">
         <v>70</v>
@@ -42980,59 +43563,65 @@
     </row>
     <row r="885" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A885" s="3" t="s">
-        <v>3110</v>
+        <v>3156</v>
       </c>
       <c r="B885" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C885" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D885" s="3" t="s">
+        <v>3157</v>
+      </c>
+      <c r="E885" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F885" s="3" t="s">
+        <v>3158</v>
+      </c>
+      <c r="G885" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H885" s="3">
         <v>78</v>
       </c>
-      <c r="C885" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D885" s="3" t="s">
-        <v>3111</v>
-      </c>
-      <c r="E885" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F885" s="3" t="s">
-        <v>2063</v>
-      </c>
-      <c r="G885" s="3"/>
-      <c r="H885" s="3">
-        <v>70</v>
-      </c>
       <c r="I885" s="3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J885" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K885" s="3"/>
-      <c r="L885" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K885" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L885" s="3" t="s">
+        <v>3159</v>
+      </c>
       <c r="M885" s="3"/>
     </row>
     <row r="886" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A886" s="3" t="s">
-        <v>3112</v>
+        <v>3160</v>
       </c>
       <c r="B886" s="3" t="s">
-        <v>196</v>
+        <v>140</v>
       </c>
       <c r="C886" s="3" t="s">
-        <v>197</v>
+        <v>3010</v>
       </c>
       <c r="D886" s="3" t="s">
-        <v>3113</v>
+        <v>3161</v>
       </c>
       <c r="E886" s="3" t="s">
-        <v>3114</v>
+        <v>68</v>
       </c>
       <c r="F886" s="3" t="s">
-        <v>2356</v>
+        <v>2075</v>
       </c>
       <c r="G886" s="3"/>
       <c r="H886" s="3">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I886" s="3"/>
       <c r="J886" s="3" t="s">
@@ -43044,29 +43633,29 @@
     </row>
     <row r="887" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A887" s="3" t="s">
-        <v>3115</v>
+        <v>3162</v>
       </c>
       <c r="B887" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C887" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D887" s="3" t="s">
-        <v>3116</v>
+        <v>3163</v>
       </c>
       <c r="E887" s="3" t="s">
-        <v>2016</v>
+        <v>68</v>
       </c>
       <c r="F887" s="3" t="s">
-        <v>3053</v>
+        <v>2063</v>
       </c>
       <c r="G887" s="3"/>
       <c r="H887" s="3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I887" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J887" s="3" t="s">
         <v>70</v>
@@ -43077,30 +43666,30 @@
     </row>
     <row r="888" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A888" s="3" t="s">
-        <v>3117</v>
+        <v>3164</v>
       </c>
       <c r="B888" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C888" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D888" s="3" t="s">
-        <v>3118</v>
+        <v>3165</v>
       </c>
       <c r="E888" s="3" t="s">
-        <v>19</v>
+        <v>306</v>
       </c>
       <c r="F888" s="3" t="s">
-        <v>1211</v>
-      </c>
-      <c r="G888" s="3"/>
+        <v>444</v>
+      </c>
+      <c r="G888" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H888" s="3">
-        <v>62</v>
-      </c>
-      <c r="I888" s="3">
-        <v>60</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I888" s="3"/>
       <c r="J888" s="3" t="s">
         <v>70</v>
       </c>
@@ -43110,30 +43699,28 @@
     </row>
     <row r="889" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A889" s="3" t="s">
-        <v>3119</v>
+        <v>3166</v>
       </c>
       <c r="B889" s="3" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="C889" s="3" t="s">
-        <v>73</v>
+        <v>3010</v>
       </c>
       <c r="D889" s="3" t="s">
-        <v>3120</v>
+        <v>3167</v>
       </c>
       <c r="E889" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F889" s="3" t="s">
-        <v>3121</v>
+        <v>3168</v>
       </c>
       <c r="G889" s="3"/>
       <c r="H889" s="3">
-        <v>54</v>
-      </c>
-      <c r="I889" s="3">
-        <v>60</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="I889" s="3"/>
       <c r="J889" s="3" t="s">
         <v>70</v>
       </c>
@@ -43143,28 +43730,30 @@
     </row>
     <row r="890" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A890" s="3" t="s">
-        <v>3119</v>
+        <v>3169</v>
       </c>
       <c r="B890" s="3" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="C890" s="3" t="s">
-        <v>54</v>
+        <v>3010</v>
       </c>
       <c r="D890" s="3" t="s">
-        <v>3122</v>
+        <v>3170</v>
       </c>
       <c r="E890" s="3" t="s">
-        <v>2016</v>
+        <v>68</v>
       </c>
       <c r="F890" s="3" t="s">
-        <v>1046</v>
+        <v>3171</v>
       </c>
       <c r="G890" s="3"/>
       <c r="H890" s="3">
-        <v>57</v>
-      </c>
-      <c r="I890" s="3"/>
+        <v>60</v>
+      </c>
+      <c r="I890" s="3">
+        <v>60</v>
+      </c>
       <c r="J890" s="3" t="s">
         <v>70</v>
       </c>
@@ -43174,29 +43763,29 @@
     </row>
     <row r="891" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A891" s="3" t="s">
-        <v>3123</v>
+        <v>3172</v>
       </c>
       <c r="B891" s="3" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="C891" s="3" t="s">
-        <v>54</v>
+        <v>3010</v>
       </c>
       <c r="D891" s="3" t="s">
-        <v>3124</v>
+        <v>3173</v>
       </c>
       <c r="E891" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F891" s="3" t="s">
-        <v>2481</v>
+        <v>3174</v>
       </c>
       <c r="G891" s="3"/>
       <c r="H891" s="3">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I891" s="3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J891" s="3" t="s">
         <v>70</v>
@@ -43207,26 +43796,26 @@
     </row>
     <row r="892" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A892" s="3" t="s">
-        <v>3125</v>
+        <v>3175</v>
       </c>
       <c r="B892" s="3" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="C892" s="3" t="s">
-        <v>54</v>
+        <v>3010</v>
       </c>
       <c r="D892" s="3" t="s">
-        <v>3126</v>
+        <v>3176</v>
       </c>
       <c r="E892" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F892" s="3" t="s">
-        <v>3127</v>
+        <v>1796</v>
       </c>
       <c r="G892" s="3"/>
       <c r="H892" s="3">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="I892" s="3"/>
       <c r="J892" s="3" t="s">
@@ -43238,28 +43827,30 @@
     </row>
     <row r="893" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A893" s="3" t="s">
-        <v>3128</v>
+        <v>3177</v>
       </c>
       <c r="B893" s="3" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="C893" s="3" t="s">
-        <v>54</v>
+        <v>3010</v>
       </c>
       <c r="D893" s="3" t="s">
-        <v>3129</v>
+        <v>3178</v>
       </c>
       <c r="E893" s="3" t="s">
-        <v>3114</v>
+        <v>68</v>
       </c>
       <c r="F893" s="3" t="s">
-        <v>3130</v>
+        <v>3179</v>
       </c>
       <c r="G893" s="3"/>
       <c r="H893" s="3">
-        <v>73</v>
-      </c>
-      <c r="I893" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="I893" s="3">
+        <v>55</v>
+      </c>
       <c r="J893" s="3" t="s">
         <v>70</v>
       </c>
@@ -43269,61 +43860,65 @@
     </row>
     <row r="894" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A894" s="3" t="s">
-        <v>3131</v>
+        <v>3180</v>
       </c>
       <c r="B894" s="3" t="s">
-        <v>178</v>
+        <v>667</v>
       </c>
       <c r="C894" s="3" t="s">
-        <v>179</v>
+        <v>668</v>
       </c>
       <c r="D894" s="3" t="s">
-        <v>3132</v>
+        <v>3181</v>
       </c>
       <c r="E894" s="3" t="s">
-        <v>3114</v>
+        <v>245</v>
       </c>
       <c r="F894" s="3" t="s">
-        <v>3133</v>
-      </c>
-      <c r="G894" s="3"/>
+        <v>289</v>
+      </c>
+      <c r="G894" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H894" s="3">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="I894" s="3"/>
       <c r="J894" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K894" s="3"/>
-      <c r="L894" s="3"/>
-      <c r="M894" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K894" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L894" s="3" t="s">
+        <v>3182</v>
+      </c>
+      <c r="M894" s="3" t="s">
+        <v>3183</v>
+      </c>
     </row>
     <row r="895" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A895" s="3" t="s">
-        <v>3134</v>
+        <v>3184</v>
       </c>
       <c r="B895" s="3" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="C895" s="3" t="s">
-        <v>54</v>
+        <v>3010</v>
       </c>
       <c r="D895" s="3" t="s">
-        <v>3135</v>
+        <v>3185</v>
       </c>
       <c r="E895" s="3" t="s">
-        <v>2016</v>
+        <v>68</v>
       </c>
       <c r="F895" s="3" t="s">
-        <v>3136</v>
+        <v>397</v>
       </c>
       <c r="G895" s="3"/>
-      <c r="H895" s="3">
-        <v>34</v>
-      </c>
-      <c r="I895" s="3">
-        <v>65</v>
-      </c>
+      <c r="H895" s="3"/>
+      <c r="I895" s="3"/>
       <c r="J895" s="3" t="s">
         <v>70</v>
       </c>
@@ -43333,30 +43928,28 @@
     </row>
     <row r="896" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A896" s="3" t="s">
-        <v>3137</v>
+        <v>3186</v>
       </c>
       <c r="B896" s="3" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="C896" s="3" t="s">
-        <v>54</v>
+        <v>3010</v>
       </c>
       <c r="D896" s="3" t="s">
-        <v>3138</v>
+        <v>3187</v>
       </c>
       <c r="E896" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F896" s="3" t="s">
-        <v>3139</v>
+        <v>170</v>
       </c>
       <c r="G896" s="3"/>
       <c r="H896" s="3">
-        <v>72</v>
-      </c>
-      <c r="I896" s="3">
-        <v>70</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="I896" s="3"/>
       <c r="J896" s="3" t="s">
         <v>70</v>
       </c>
@@ -43366,38 +43959,46 @@
     </row>
     <row r="897" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A897" s="3" t="s">
-        <v>3140</v>
+        <v>3188</v>
       </c>
       <c r="B897" s="3" t="s">
-        <v>909</v>
+        <v>2613</v>
       </c>
       <c r="C897" s="3" t="s">
-        <v>910</v>
+        <v>2614</v>
       </c>
       <c r="D897" s="3" t="s">
-        <v>3141</v>
+        <v>3189</v>
       </c>
       <c r="E897" s="3" t="s">
-        <v>2016</v>
+        <v>19</v>
       </c>
       <c r="F897" s="3" t="s">
-        <v>1866</v>
-      </c>
-      <c r="G897" s="3"/>
+        <v>3058</v>
+      </c>
+      <c r="G897" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H897" s="3">
-        <v>33</v>
-      </c>
-      <c r="I897" s="3"/>
+        <v>68</v>
+      </c>
+      <c r="I897" s="3">
+        <v>65</v>
+      </c>
       <c r="J897" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K897" s="3"/>
-      <c r="L897" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K897" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L897" s="3" t="s">
+        <v>3190</v>
+      </c>
       <c r="M897" s="3"/>
     </row>
     <row r="898" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A898" s="3" t="s">
-        <v>3142</v>
+        <v>3191</v>
       </c>
       <c r="B898" s="3" t="s">
         <v>34</v>
@@ -43406,53 +44007,59 @@
         <v>35</v>
       </c>
       <c r="D898" s="3" t="s">
-        <v>3143</v>
+        <v>3192</v>
       </c>
       <c r="E898" s="3" t="s">
-        <v>306</v>
+        <v>245</v>
       </c>
       <c r="F898" s="3" t="s">
-        <v>3144</v>
-      </c>
-      <c r="G898" s="3"/>
+        <v>134</v>
+      </c>
+      <c r="G898" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H898" s="3">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="I898" s="3">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="J898" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K898" s="3"/>
-      <c r="L898" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K898" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L898" s="3" t="s">
+        <v>3193</v>
+      </c>
       <c r="M898" s="3"/>
     </row>
     <row r="899" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A899" s="3" t="s">
-        <v>3145</v>
+        <v>3194</v>
       </c>
       <c r="B899" s="3" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="C899" s="3" t="s">
-        <v>35</v>
+        <v>3010</v>
       </c>
       <c r="D899" s="3" t="s">
-        <v>3146</v>
+        <v>3195</v>
       </c>
       <c r="E899" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F899" s="3" t="s">
-        <v>3147</v>
+        <v>3196</v>
       </c>
       <c r="G899" s="3"/>
       <c r="H899" s="3">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="I899" s="3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J899" s="3" t="s">
         <v>70</v>
@@ -43463,29 +44070,29 @@
     </row>
     <row r="900" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A900" s="3" t="s">
-        <v>3148</v>
+        <v>3197</v>
       </c>
       <c r="B900" s="3" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="C900" s="3" t="s">
-        <v>35</v>
+        <v>3010</v>
       </c>
       <c r="D900" s="3" t="s">
-        <v>3149</v>
+        <v>3198</v>
       </c>
       <c r="E900" s="3" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F900" s="3" t="s">
-        <v>783</v>
+        <v>2044</v>
       </c>
       <c r="G900" s="3"/>
       <c r="H900" s="3">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="I900" s="3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="J900" s="3" t="s">
         <v>70</v>
@@ -43496,61 +44103,67 @@
     </row>
     <row r="901" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A901" s="3" t="s">
-        <v>3150</v>
+        <v>3199</v>
       </c>
       <c r="B901" s="3" t="s">
-        <v>34</v>
+        <v>2613</v>
       </c>
       <c r="C901" s="3" t="s">
-        <v>35</v>
+        <v>2614</v>
       </c>
       <c r="D901" s="3" t="s">
-        <v>3151</v>
+        <v>3200</v>
       </c>
       <c r="E901" s="3" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="F901" s="3" t="s">
-        <v>1372</v>
-      </c>
-      <c r="G901" s="3"/>
+        <v>3201</v>
+      </c>
+      <c r="G901" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H901" s="3">
-        <v>57</v>
-      </c>
-      <c r="I901" s="3">
-        <v>55</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="I901" s="3"/>
       <c r="J901" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K901" s="3"/>
-      <c r="L901" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="K901" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L901" s="3" t="s">
+        <v>3202</v>
+      </c>
       <c r="M901" s="3"/>
     </row>
     <row r="902" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A902" s="3" t="s">
-        <v>3152</v>
+        <v>3203</v>
       </c>
       <c r="B902" s="3" t="s">
-        <v>34</v>
+        <v>140</v>
       </c>
       <c r="C902" s="3" t="s">
-        <v>35</v>
+        <v>3010</v>
       </c>
       <c r="D902" s="3" t="s">
-        <v>3153</v>
+        <v>3204</v>
       </c>
       <c r="E902" s="3" t="s">
-        <v>306</v>
+        <v>68</v>
       </c>
       <c r="F902" s="3" t="s">
-        <v>257</v>
+        <v>3205</v>
       </c>
       <c r="G902" s="3"/>
       <c r="H902" s="3">
-        <v>25</v>
-      </c>
-      <c r="I902" s="3"/>
+        <v>43</v>
+      </c>
+      <c r="I902" s="3">
+        <v>45</v>
+      </c>
       <c r="J902" s="3" t="s">
         <v>70</v>
       </c>
@@ -43560,29 +44173,29 @@
     </row>
     <row r="903" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A903" s="3" t="s">
-        <v>3154</v>
+        <v>3206</v>
       </c>
       <c r="B903" s="3" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="C903" s="3" t="s">
-        <v>73</v>
+        <v>3010</v>
       </c>
       <c r="D903" s="3" t="s">
-        <v>3155</v>
+        <v>3207</v>
       </c>
       <c r="E903" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="F903" s="3" t="s">
-        <v>3156</v>
+        <v>1969</v>
       </c>
       <c r="G903" s="3"/>
       <c r="H903" s="3">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="I903" s="3">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="J903" s="3" t="s">
         <v>70</v>
@@ -43593,26 +44206,26 @@
     </row>
     <row r="904" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A904" s="3" t="s">
-        <v>3157</v>
+        <v>3208</v>
       </c>
       <c r="B904" s="3" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="C904" s="3" t="s">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="D904" s="3" t="s">
-        <v>3158</v>
+        <v>3209</v>
       </c>
       <c r="E904" s="3" t="s">
-        <v>19</v>
+        <v>3210</v>
       </c>
       <c r="F904" s="3" t="s">
-        <v>2824</v>
+        <v>1000</v>
       </c>
       <c r="G904" s="3"/>
       <c r="H904" s="3">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I904" s="3">
         <v>55</v>
@@ -43623,6 +44236,902 @@
       <c r="K904" s="3"/>
       <c r="L904" s="3"/>
       <c r="M904" s="3"/>
+    </row>
+    <row r="905" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A905" s="3" t="s">
+        <v>3211</v>
+      </c>
+      <c r="B905" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C905" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D905" s="3" t="s">
+        <v>3212</v>
+      </c>
+      <c r="E905" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="F905" s="3" t="s">
+        <v>2748</v>
+      </c>
+      <c r="G905" s="3"/>
+      <c r="H905" s="3">
+        <v>27</v>
+      </c>
+      <c r="I905" s="3"/>
+      <c r="J905" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K905" s="3"/>
+      <c r="L905" s="3"/>
+      <c r="M905" s="3"/>
+    </row>
+    <row r="906" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A906" s="3" t="s">
+        <v>3213</v>
+      </c>
+      <c r="B906" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C906" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D906" s="3" t="s">
+        <v>3214</v>
+      </c>
+      <c r="E906" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F906" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="G906" s="3"/>
+      <c r="H906" s="3">
+        <v>62</v>
+      </c>
+      <c r="I906" s="3">
+        <v>55</v>
+      </c>
+      <c r="J906" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K906" s="3"/>
+      <c r="L906" s="3"/>
+      <c r="M906" s="3"/>
+    </row>
+    <row r="907" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A907" s="3" t="s">
+        <v>3215</v>
+      </c>
+      <c r="B907" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C907" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D907" s="3" t="s">
+        <v>3216</v>
+      </c>
+      <c r="E907" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F907" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G907" s="3"/>
+      <c r="H907" s="3">
+        <v>49</v>
+      </c>
+      <c r="I907" s="3"/>
+      <c r="J907" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K907" s="3"/>
+      <c r="L907" s="3"/>
+      <c r="M907" s="3"/>
+    </row>
+    <row r="908" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A908" s="3" t="s">
+        <v>3217</v>
+      </c>
+      <c r="B908" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C908" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D908" s="3" t="s">
+        <v>3218</v>
+      </c>
+      <c r="E908" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F908" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="G908" s="3"/>
+      <c r="H908" s="3">
+        <v>70</v>
+      </c>
+      <c r="I908" s="3">
+        <v>60</v>
+      </c>
+      <c r="J908" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K908" s="3"/>
+      <c r="L908" s="3"/>
+      <c r="M908" s="3"/>
+    </row>
+    <row r="909" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A909" s="3" t="s">
+        <v>3219</v>
+      </c>
+      <c r="B909" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C909" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D909" s="3" t="s">
+        <v>3220</v>
+      </c>
+      <c r="E909" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F909" s="3" t="s">
+        <v>3221</v>
+      </c>
+      <c r="G909" s="3"/>
+      <c r="H909" s="3">
+        <v>64</v>
+      </c>
+      <c r="I909" s="3">
+        <v>60</v>
+      </c>
+      <c r="J909" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K909" s="3"/>
+      <c r="L909" s="3"/>
+      <c r="M909" s="3"/>
+    </row>
+    <row r="910" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A910" s="3" t="s">
+        <v>3219</v>
+      </c>
+      <c r="B910" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C910" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D910" s="3" t="s">
+        <v>3222</v>
+      </c>
+      <c r="E910" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F910" s="3" t="s">
+        <v>3223</v>
+      </c>
+      <c r="G910" s="3"/>
+      <c r="H910" s="3">
+        <v>67</v>
+      </c>
+      <c r="I910" s="3">
+        <v>60</v>
+      </c>
+      <c r="J910" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K910" s="3"/>
+      <c r="L910" s="3"/>
+      <c r="M910" s="3"/>
+    </row>
+    <row r="911" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A911" s="3" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B911" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C911" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D911" s="3" t="s">
+        <v>3225</v>
+      </c>
+      <c r="E911" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F911" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="G911" s="3"/>
+      <c r="H911" s="3">
+        <v>62</v>
+      </c>
+      <c r="I911" s="3">
+        <v>60</v>
+      </c>
+      <c r="J911" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K911" s="3"/>
+      <c r="L911" s="3"/>
+      <c r="M911" s="3"/>
+    </row>
+    <row r="912" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A912" s="3" t="s">
+        <v>3226</v>
+      </c>
+      <c r="B912" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C912" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D912" s="3" t="s">
+        <v>3227</v>
+      </c>
+      <c r="E912" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F912" s="3" t="s">
+        <v>3228</v>
+      </c>
+      <c r="G912" s="3"/>
+      <c r="H912" s="3">
+        <v>71</v>
+      </c>
+      <c r="I912" s="3">
+        <v>65</v>
+      </c>
+      <c r="J912" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K912" s="3"/>
+      <c r="L912" s="3"/>
+      <c r="M912" s="3"/>
+    </row>
+    <row r="913" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A913" s="3" t="s">
+        <v>3229</v>
+      </c>
+      <c r="B913" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C913" s="3" t="s">
+        <v>3010</v>
+      </c>
+      <c r="D913" s="3" t="s">
+        <v>3230</v>
+      </c>
+      <c r="E913" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F913" s="3" t="s">
+        <v>3231</v>
+      </c>
+      <c r="G913" s="3"/>
+      <c r="H913" s="3">
+        <v>66</v>
+      </c>
+      <c r="I913" s="3">
+        <v>55</v>
+      </c>
+      <c r="J913" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K913" s="3"/>
+      <c r="L913" s="3"/>
+      <c r="M913" s="3"/>
+    </row>
+    <row r="914" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A914" s="3" t="s">
+        <v>3232</v>
+      </c>
+      <c r="B914" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C914" s="3" t="s">
+        <v>3010</v>
+      </c>
+      <c r="D914" s="3" t="s">
+        <v>3233</v>
+      </c>
+      <c r="E914" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F914" s="3" t="s">
+        <v>3234</v>
+      </c>
+      <c r="G914" s="3"/>
+      <c r="H914" s="3">
+        <v>29</v>
+      </c>
+      <c r="I914" s="3">
+        <v>35</v>
+      </c>
+      <c r="J914" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K914" s="3"/>
+      <c r="L914" s="3"/>
+      <c r="M914" s="3"/>
+    </row>
+    <row r="915" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A915" s="3" t="s">
+        <v>3235</v>
+      </c>
+      <c r="B915" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C915" s="3" t="s">
+        <v>2614</v>
+      </c>
+      <c r="D915" s="3" t="s">
+        <v>3236</v>
+      </c>
+      <c r="E915" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F915" s="3" t="s">
+        <v>3237</v>
+      </c>
+      <c r="G915" s="3"/>
+      <c r="H915" s="3">
+        <v>39</v>
+      </c>
+      <c r="I915" s="3">
+        <v>55</v>
+      </c>
+      <c r="J915" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K915" s="3"/>
+      <c r="L915" s="3"/>
+      <c r="M915" s="3"/>
+    </row>
+    <row r="916" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A916" s="3" t="s">
+        <v>3238</v>
+      </c>
+      <c r="B916" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C916" s="3" t="s">
+        <v>2614</v>
+      </c>
+      <c r="D916" s="3" t="s">
+        <v>3239</v>
+      </c>
+      <c r="E916" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F916" s="3" t="s">
+        <v>3240</v>
+      </c>
+      <c r="G916" s="3"/>
+      <c r="H916" s="3">
+        <v>37</v>
+      </c>
+      <c r="I916" s="3"/>
+      <c r="J916" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K916" s="3"/>
+      <c r="L916" s="3"/>
+      <c r="M916" s="3"/>
+    </row>
+    <row r="917" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A917" s="3" t="s">
+        <v>3241</v>
+      </c>
+      <c r="B917" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C917" s="3" t="s">
+        <v>2614</v>
+      </c>
+      <c r="D917" s="3" t="s">
+        <v>3242</v>
+      </c>
+      <c r="E917" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F917" s="3" t="s">
+        <v>3243</v>
+      </c>
+      <c r="G917" s="3"/>
+      <c r="H917" s="3">
+        <v>6</v>
+      </c>
+      <c r="I917" s="3"/>
+      <c r="J917" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K917" s="3"/>
+      <c r="L917" s="3"/>
+      <c r="M917" s="3"/>
+    </row>
+    <row r="918" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A918" s="3" t="s">
+        <v>3244</v>
+      </c>
+      <c r="B918" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C918" s="3" t="s">
+        <v>2614</v>
+      </c>
+      <c r="D918" s="3" t="s">
+        <v>3245</v>
+      </c>
+      <c r="E918" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F918" s="3" t="s">
+        <v>3246</v>
+      </c>
+      <c r="G918" s="3"/>
+      <c r="H918" s="3">
+        <v>27</v>
+      </c>
+      <c r="I918" s="3"/>
+      <c r="J918" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K918" s="3"/>
+      <c r="L918" s="3"/>
+      <c r="M918" s="3"/>
+    </row>
+    <row r="919" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A919" s="3" t="s">
+        <v>3247</v>
+      </c>
+      <c r="B919" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C919" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="D919" s="3" t="s">
+        <v>3248</v>
+      </c>
+      <c r="E919" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="F919" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G919" s="3"/>
+      <c r="H919" s="3">
+        <v>23</v>
+      </c>
+      <c r="I919" s="3"/>
+      <c r="J919" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K919" s="3"/>
+      <c r="L919" s="3"/>
+      <c r="M919" s="3"/>
+    </row>
+    <row r="920" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A920" s="3" t="s">
+        <v>3249</v>
+      </c>
+      <c r="B920" s="3" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C920" s="3" t="s">
+        <v>2614</v>
+      </c>
+      <c r="D920" s="3" t="s">
+        <v>3250</v>
+      </c>
+      <c r="E920" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F920" s="3" t="s">
+        <v>2582</v>
+      </c>
+      <c r="G920" s="3"/>
+      <c r="H920" s="3">
+        <v>46</v>
+      </c>
+      <c r="I920" s="3"/>
+      <c r="J920" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K920" s="3"/>
+      <c r="L920" s="3"/>
+      <c r="M920" s="3"/>
+    </row>
+    <row r="921" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A921" s="3" t="s">
+        <v>3251</v>
+      </c>
+      <c r="B921" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C921" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D921" s="3" t="s">
+        <v>3252</v>
+      </c>
+      <c r="E921" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F921" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="G921" s="3"/>
+      <c r="H921" s="3">
+        <v>32</v>
+      </c>
+      <c r="I921" s="3"/>
+      <c r="J921" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K921" s="3"/>
+      <c r="L921" s="3"/>
+      <c r="M921" s="3"/>
+    </row>
+    <row r="922" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A922" s="3" t="s">
+        <v>3253</v>
+      </c>
+      <c r="B922" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="C922" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="D922" s="3" t="s">
+        <v>3254</v>
+      </c>
+      <c r="E922" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F922" s="3" t="s">
+        <v>3255</v>
+      </c>
+      <c r="G922" s="3"/>
+      <c r="H922" s="3">
+        <v>67</v>
+      </c>
+      <c r="I922" s="3">
+        <v>70</v>
+      </c>
+      <c r="J922" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K922" s="3"/>
+      <c r="L922" s="3"/>
+      <c r="M922" s="3"/>
+    </row>
+    <row r="923" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A923" s="3" t="s">
+        <v>3256</v>
+      </c>
+      <c r="B923" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="C923" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="D923" s="3" t="s">
+        <v>3257</v>
+      </c>
+      <c r="E923" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F923" s="3" t="s">
+        <v>3258</v>
+      </c>
+      <c r="G923" s="3"/>
+      <c r="H923" s="3">
+        <v>79</v>
+      </c>
+      <c r="I923" s="3">
+        <v>70</v>
+      </c>
+      <c r="J923" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K923" s="3"/>
+      <c r="L923" s="3"/>
+      <c r="M923" s="3"/>
+    </row>
+    <row r="924" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A924" s="3" t="s">
+        <v>3256</v>
+      </c>
+      <c r="B924" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="C924" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="D924" s="3" t="s">
+        <v>3259</v>
+      </c>
+      <c r="E924" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F924" s="3" t="s">
+        <v>3260</v>
+      </c>
+      <c r="G924" s="3"/>
+      <c r="H924" s="3">
+        <v>76</v>
+      </c>
+      <c r="I924" s="3">
+        <v>70</v>
+      </c>
+      <c r="J924" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K924" s="3"/>
+      <c r="L924" s="3"/>
+      <c r="M924" s="3"/>
+    </row>
+    <row r="925" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A925" s="3" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B925" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C925" s="3" t="s">
+        <v>3010</v>
+      </c>
+      <c r="D925" s="3" t="s">
+        <v>3262</v>
+      </c>
+      <c r="E925" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F925" s="3" t="s">
+        <v>3263</v>
+      </c>
+      <c r="G925" s="3"/>
+      <c r="H925" s="3">
+        <v>23</v>
+      </c>
+      <c r="I925" s="3">
+        <v>60</v>
+      </c>
+      <c r="J925" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K925" s="3"/>
+      <c r="L925" s="3"/>
+      <c r="M925" s="3"/>
+    </row>
+    <row r="926" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A926" s="3" t="s">
+        <v>3264</v>
+      </c>
+      <c r="B926" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C926" s="3" t="s">
+        <v>3010</v>
+      </c>
+      <c r="D926" s="3" t="s">
+        <v>3265</v>
+      </c>
+      <c r="E926" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F926" s="3" t="s">
+        <v>3266</v>
+      </c>
+      <c r="G926" s="3"/>
+      <c r="H926" s="3"/>
+      <c r="I926" s="3"/>
+      <c r="J926" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K926" s="3"/>
+      <c r="L926" s="3"/>
+      <c r="M926" s="3"/>
+    </row>
+    <row r="927" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A927" s="3" t="s">
+        <v>3267</v>
+      </c>
+      <c r="B927" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C927" s="3" t="s">
+        <v>3010</v>
+      </c>
+      <c r="D927" s="3" t="s">
+        <v>3268</v>
+      </c>
+      <c r="E927" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F927" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="G927" s="3"/>
+      <c r="H927" s="3">
+        <v>72</v>
+      </c>
+      <c r="I927" s="3">
+        <v>70</v>
+      </c>
+      <c r="J927" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K927" s="3"/>
+      <c r="L927" s="3"/>
+      <c r="M927" s="3"/>
+    </row>
+    <row r="928" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A928" s="3" t="s">
+        <v>3269</v>
+      </c>
+      <c r="B928" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C928" s="3" t="s">
+        <v>3010</v>
+      </c>
+      <c r="D928" s="3" t="s">
+        <v>3270</v>
+      </c>
+      <c r="E928" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F928" s="3" t="s">
+        <v>3271</v>
+      </c>
+      <c r="G928" s="3"/>
+      <c r="H928" s="3">
+        <v>36</v>
+      </c>
+      <c r="I928" s="3"/>
+      <c r="J928" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K928" s="3"/>
+      <c r="L928" s="3"/>
+      <c r="M928" s="3"/>
+    </row>
+    <row r="929" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A929" s="3" t="s">
+        <v>3272</v>
+      </c>
+      <c r="B929" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C929" s="3" t="s">
+        <v>3010</v>
+      </c>
+      <c r="D929" s="3" t="s">
+        <v>3273</v>
+      </c>
+      <c r="E929" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F929" s="3" t="s">
+        <v>3274</v>
+      </c>
+      <c r="G929" s="3"/>
+      <c r="H929" s="3">
+        <v>45</v>
+      </c>
+      <c r="I929" s="3"/>
+      <c r="J929" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K929" s="3"/>
+      <c r="L929" s="3"/>
+      <c r="M929" s="3"/>
+    </row>
+    <row r="930" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A930" s="3" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B930" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C930" s="3" t="s">
+        <v>3010</v>
+      </c>
+      <c r="D930" s="3" t="s">
+        <v>3276</v>
+      </c>
+      <c r="E930" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F930" s="3" t="s">
+        <v>3277</v>
+      </c>
+      <c r="G930" s="3"/>
+      <c r="H930" s="3">
+        <v>16</v>
+      </c>
+      <c r="I930" s="3"/>
+      <c r="J930" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K930" s="3"/>
+      <c r="L930" s="3"/>
+      <c r="M930" s="3"/>
+    </row>
+    <row r="931" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A931" s="3" t="s">
+        <v>3278</v>
+      </c>
+      <c r="B931" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C931" s="3" t="s">
+        <v>3010</v>
+      </c>
+      <c r="D931" s="3" t="s">
+        <v>3279</v>
+      </c>
+      <c r="E931" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F931" s="3" t="s">
+        <v>2814</v>
+      </c>
+      <c r="G931" s="3"/>
+      <c r="H931" s="3">
+        <v>36</v>
+      </c>
+      <c r="I931" s="3">
+        <v>65</v>
+      </c>
+      <c r="J931" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K931" s="3"/>
+      <c r="L931" s="3"/>
+      <c r="M931" s="3"/>
+    </row>
+    <row r="932" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A932" s="3" t="s">
+        <v>3280</v>
+      </c>
+      <c r="B932" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C932" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D932" s="3" t="s">
+        <v>3281</v>
+      </c>
+      <c r="E932" s="3" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F932" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G932" s="3"/>
+      <c r="H932" s="3">
+        <v>4</v>
+      </c>
+      <c r="I932" s="3"/>
+      <c r="J932" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K932" s="3"/>
+      <c r="L932" s="3"/>
+      <c r="M932" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
